--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/25,08,26 ПОКОМ КИ/дв 25,08,26 бррсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/25,08,26 ПОКОМ КИ/дв 25,08,26 бррсч пок ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\25,08,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3342C936-44B3-463C-9556-ED598A56FE5A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCBE0F5-A672-422B-960A-B20321D60EA3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AH$129</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1459,7 +1459,10 @@
         <f>SUM(AH6:AH499)</f>
         <v>6573</v>
       </c>
-      <c r="AI5" s="12"/>
+      <c r="AI5" s="3">
+        <f>SUM(AI6:AI499)</f>
+        <v>3192.9612000000002</v>
+      </c>
       <c r="AJ5" s="12"/>
       <c r="AK5" s="12"/>
       <c r="AL5" s="12"/>
@@ -1568,7 +1571,10 @@
         <f>ROUND(G6*T6,0)</f>
         <v>0</v>
       </c>
-      <c r="AI6" s="12"/>
+      <c r="AI6" s="12">
+        <f>R6*G6</f>
+        <v>49.53</v>
+      </c>
       <c r="AJ6" s="12"/>
       <c r="AK6" s="12"/>
       <c r="AL6" s="12"/>
@@ -1680,7 +1686,10 @@
         <f t="shared" ref="AH7:AH70" si="7">ROUND(G7*T7,0)</f>
         <v>875</v>
       </c>
-      <c r="AI7" s="12"/>
+      <c r="AI7" s="12">
+        <f t="shared" ref="AI7:AI70" si="8">R7*G7</f>
+        <v>153.03919999999999</v>
+      </c>
       <c r="AJ7" s="12"/>
       <c r="AK7" s="12"/>
       <c r="AL7" s="12"/>
@@ -1792,7 +1801,10 @@
         <f t="shared" si="7"/>
         <v>352</v>
       </c>
-      <c r="AI8" s="12"/>
+      <c r="AI8" s="12">
+        <f t="shared" si="8"/>
+        <v>112.5746</v>
+      </c>
       <c r="AJ8" s="12"/>
       <c r="AK8" s="12"/>
       <c r="AL8" s="12"/>
@@ -1891,7 +1903,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI9" s="12"/>
+      <c r="AI9" s="12">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AJ9" s="12"/>
       <c r="AK9" s="12"/>
       <c r="AL9" s="12"/>
@@ -2000,7 +2015,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI10" s="12"/>
+      <c r="AI10" s="12">
+        <f t="shared" si="8"/>
+        <v>18.720000000000002</v>
+      </c>
       <c r="AJ10" s="12"/>
       <c r="AK10" s="12"/>
       <c r="AL10" s="12"/>
@@ -2062,7 +2080,7 @@
         <v>145.4</v>
       </c>
       <c r="S11" s="4">
-        <f t="shared" ref="S11:S19" si="8">11*R11-Q11-P11-O11-F11</f>
+        <f t="shared" ref="S11:S19" si="9">11*R11-Q11-P11-O11-F11</f>
         <v>31.698000000000093</v>
       </c>
       <c r="T11" s="4">
@@ -2112,7 +2130,10 @@
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
-      <c r="AI11" s="12"/>
+      <c r="AI11" s="12">
+        <f t="shared" si="8"/>
+        <v>65.430000000000007</v>
+      </c>
       <c r="AJ11" s="12"/>
       <c r="AK11" s="12"/>
       <c r="AL11" s="12"/>
@@ -2221,7 +2242,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI12" s="12"/>
+      <c r="AI12" s="12">
+        <f t="shared" si="8"/>
+        <v>1.53</v>
+      </c>
       <c r="AJ12" s="12"/>
       <c r="AK12" s="12"/>
       <c r="AL12" s="12"/>
@@ -2332,7 +2356,10 @@
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="AI13" s="12"/>
+      <c r="AI13" s="12">
+        <f t="shared" si="8"/>
+        <v>4.8599999999999994</v>
+      </c>
       <c r="AJ13" s="12"/>
       <c r="AK13" s="12"/>
       <c r="AL13" s="12"/>
@@ -2394,7 +2421,7 @@
         <v>54.4</v>
       </c>
       <c r="S14" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>238.39999999999998</v>
       </c>
       <c r="T14" s="4">
@@ -2444,7 +2471,10 @@
         <f t="shared" si="7"/>
         <v>41</v>
       </c>
-      <c r="AI14" s="12"/>
+      <c r="AI14" s="12">
+        <f t="shared" si="8"/>
+        <v>9.2480000000000011</v>
+      </c>
       <c r="AJ14" s="12"/>
       <c r="AK14" s="12"/>
       <c r="AL14" s="12"/>
@@ -2506,7 +2536,7 @@
         <v>84.37</v>
       </c>
       <c r="S15" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>327.32030199999997</v>
       </c>
       <c r="T15" s="4">
@@ -2556,7 +2586,10 @@
         <f t="shared" si="7"/>
         <v>327</v>
       </c>
-      <c r="AI15" s="12"/>
+      <c r="AI15" s="12">
+        <f t="shared" si="8"/>
+        <v>84.37</v>
+      </c>
       <c r="AJ15" s="12"/>
       <c r="AK15" s="12"/>
       <c r="AL15" s="12"/>
@@ -2620,7 +2653,7 @@
         <v>435.88019999999995</v>
       </c>
       <c r="S16" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>627.85371399999917</v>
       </c>
       <c r="T16" s="4">
@@ -2669,7 +2702,10 @@
         <f t="shared" si="7"/>
         <v>550</v>
       </c>
-      <c r="AI16" s="12"/>
+      <c r="AI16" s="12">
+        <f t="shared" si="8"/>
+        <v>435.88019999999995</v>
+      </c>
       <c r="AJ16" s="12"/>
       <c r="AK16" s="12"/>
       <c r="AL16" s="12"/>
@@ -2731,7 +2767,7 @@
         <v>13.439400000000001</v>
       </c>
       <c r="S17" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>28.906162000000023</v>
       </c>
       <c r="T17" s="4">
@@ -2781,7 +2817,10 @@
         <f t="shared" si="7"/>
         <v>29</v>
       </c>
-      <c r="AI17" s="12"/>
+      <c r="AI17" s="12">
+        <f t="shared" si="8"/>
+        <v>13.439400000000001</v>
+      </c>
       <c r="AJ17" s="12"/>
       <c r="AK17" s="12"/>
       <c r="AL17" s="12"/>
@@ -2841,7 +2880,7 @@
         <v>8.6264000000000003</v>
       </c>
       <c r="S18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>21.379800000000003</v>
       </c>
       <c r="T18" s="4">
@@ -2891,7 +2930,10 @@
         <f t="shared" si="7"/>
         <v>21</v>
       </c>
-      <c r="AI18" s="12"/>
+      <c r="AI18" s="12">
+        <f t="shared" si="8"/>
+        <v>8.6264000000000003</v>
+      </c>
       <c r="AJ18" s="12"/>
       <c r="AK18" s="12"/>
       <c r="AL18" s="12"/>
@@ -2953,7 +2995,7 @@
         <v>5.7140000000000004</v>
       </c>
       <c r="S19" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>16.924000000000028</v>
       </c>
       <c r="T19" s="4">
@@ -3003,7 +3045,10 @@
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
-      <c r="AI19" s="12"/>
+      <c r="AI19" s="12">
+        <f t="shared" si="8"/>
+        <v>5.7140000000000004</v>
+      </c>
       <c r="AJ19" s="12"/>
       <c r="AK19" s="12"/>
       <c r="AL19" s="12"/>
@@ -3112,7 +3157,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI20" s="12"/>
+      <c r="AI20" s="12">
+        <f t="shared" si="8"/>
+        <v>58.342399999999998</v>
+      </c>
       <c r="AJ20" s="12"/>
       <c r="AK20" s="12"/>
       <c r="AL20" s="12"/>
@@ -3224,7 +3272,10 @@
         <f t="shared" si="7"/>
         <v>162</v>
       </c>
-      <c r="AI21" s="12"/>
+      <c r="AI21" s="12">
+        <f t="shared" si="8"/>
+        <v>26.132600000000004</v>
+      </c>
       <c r="AJ21" s="12"/>
       <c r="AK21" s="12"/>
       <c r="AL21" s="12"/>
@@ -3337,7 +3388,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AI22" s="12"/>
+      <c r="AI22" s="12">
+        <f t="shared" si="8"/>
+        <v>29.136800000000001</v>
+      </c>
       <c r="AJ22" s="12"/>
       <c r="AK22" s="12"/>
       <c r="AL22" s="12"/>
@@ -3446,7 +3500,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI23" s="12"/>
+      <c r="AI23" s="12">
+        <f t="shared" si="8"/>
+        <v>2.327</v>
+      </c>
       <c r="AJ23" s="12"/>
       <c r="AK23" s="12"/>
       <c r="AL23" s="12"/>
@@ -3559,7 +3616,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AI24" s="12"/>
+      <c r="AI24" s="12">
+        <f t="shared" si="8"/>
+        <v>39.827999999999996</v>
+      </c>
       <c r="AJ24" s="12"/>
       <c r="AK24" s="12"/>
       <c r="AL24" s="12"/>
@@ -3658,7 +3718,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI25" s="12"/>
+      <c r="AI25" s="12">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AJ25" s="12"/>
       <c r="AK25" s="12"/>
       <c r="AL25" s="12"/>
@@ -3770,7 +3833,10 @@
         <f t="shared" si="7"/>
         <v>270</v>
       </c>
-      <c r="AI26" s="12"/>
+      <c r="AI26" s="12">
+        <f t="shared" si="8"/>
+        <v>42.488399999999999</v>
+      </c>
       <c r="AJ26" s="12"/>
       <c r="AK26" s="12"/>
       <c r="AL26" s="12"/>
@@ -3881,7 +3947,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AI27" s="12"/>
+      <c r="AI27" s="12">
+        <f t="shared" si="8"/>
+        <v>-0.96479999999999999</v>
+      </c>
       <c r="AJ27" s="12"/>
       <c r="AK27" s="12"/>
       <c r="AL27" s="12"/>
@@ -3943,7 +4012,7 @@
         <v>27.609400000000001</v>
       </c>
       <c r="S28" s="4">
-        <f t="shared" ref="S28:S39" si="9">11*R28-Q28-P28-O28-F28</f>
+        <f t="shared" ref="S28:S39" si="10">11*R28-Q28-P28-O28-F28</f>
         <v>36.886399999999981</v>
       </c>
       <c r="T28" s="4">
@@ -3993,7 +4062,10 @@
         <f t="shared" si="7"/>
         <v>37</v>
       </c>
-      <c r="AI28" s="12"/>
+      <c r="AI28" s="12">
+        <f t="shared" si="8"/>
+        <v>27.609400000000001</v>
+      </c>
       <c r="AJ28" s="12"/>
       <c r="AK28" s="12"/>
       <c r="AL28" s="12"/>
@@ -4102,7 +4174,10 @@
         <f t="shared" si="7"/>
         <v>280</v>
       </c>
-      <c r="AI29" s="12"/>
+      <c r="AI29" s="12">
+        <f t="shared" si="8"/>
+        <v>-1.585</v>
+      </c>
       <c r="AJ29" s="12"/>
       <c r="AK29" s="12"/>
       <c r="AL29" s="12"/>
@@ -4207,7 +4282,10 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="AI30" s="12"/>
+      <c r="AI30" s="12">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AJ30" s="12"/>
       <c r="AK30" s="12"/>
       <c r="AL30" s="12"/>
@@ -4319,7 +4397,10 @@
         <f t="shared" si="7"/>
         <v>116</v>
       </c>
-      <c r="AI31" s="12"/>
+      <c r="AI31" s="12">
+        <f t="shared" si="8"/>
+        <v>19.2578</v>
+      </c>
       <c r="AJ31" s="12"/>
       <c r="AK31" s="12"/>
       <c r="AL31" s="12"/>
@@ -4428,7 +4509,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI32" s="12"/>
+      <c r="AI32" s="12">
+        <f t="shared" si="8"/>
+        <v>11.801600000000001</v>
+      </c>
       <c r="AJ32" s="12"/>
       <c r="AK32" s="12"/>
       <c r="AL32" s="12"/>
@@ -4538,7 +4622,10 @@
         <f t="shared" si="7"/>
         <v>124</v>
       </c>
-      <c r="AI33" s="12"/>
+      <c r="AI33" s="12">
+        <f t="shared" si="8"/>
+        <v>20.1646</v>
+      </c>
       <c r="AJ33" s="12"/>
       <c r="AK33" s="12"/>
       <c r="AL33" s="12"/>
@@ -4649,7 +4736,10 @@
         <f t="shared" si="7"/>
         <v>168</v>
       </c>
-      <c r="AI34" s="12"/>
+      <c r="AI34" s="12">
+        <f t="shared" si="8"/>
+        <v>63.52000000000001</v>
+      </c>
       <c r="AJ34" s="12"/>
       <c r="AK34" s="12"/>
       <c r="AL34" s="12"/>
@@ -4711,7 +4801,7 @@
         <v>69.400000000000006</v>
       </c>
       <c r="S35" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>329.12000000000012</v>
       </c>
       <c r="T35" s="4">
@@ -4761,7 +4851,10 @@
         <f t="shared" si="7"/>
         <v>148</v>
       </c>
-      <c r="AI35" s="12"/>
+      <c r="AI35" s="12">
+        <f t="shared" si="8"/>
+        <v>31.230000000000004</v>
+      </c>
       <c r="AJ35" s="12"/>
       <c r="AK35" s="12"/>
       <c r="AL35" s="12"/>
@@ -4828,7 +4921,7 @@
         <v>250</v>
       </c>
       <c r="T36" s="4">
-        <f t="shared" ref="T36:T37" si="10">S36*0.7</f>
+        <f t="shared" ref="T36:T37" si="11">S36*0.7</f>
         <v>175</v>
       </c>
       <c r="U36" s="12">
@@ -4874,7 +4967,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AI36" s="12"/>
+      <c r="AI36" s="12">
+        <f t="shared" si="8"/>
+        <v>24.080000000000002</v>
+      </c>
       <c r="AJ36" s="12"/>
       <c r="AK36" s="12"/>
       <c r="AL36" s="12"/>
@@ -4941,7 +5037,7 @@
         <v>60</v>
       </c>
       <c r="T37" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>42</v>
       </c>
       <c r="U37" s="12">
@@ -4987,7 +5083,10 @@
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
-      <c r="AI37" s="12"/>
+      <c r="AI37" s="12">
+        <f t="shared" si="8"/>
+        <v>5.04</v>
+      </c>
       <c r="AJ37" s="12"/>
       <c r="AK37" s="12"/>
       <c r="AL37" s="12"/>
@@ -5034,7 +5133,7 @@
         <v>77.7</v>
       </c>
       <c r="L38" s="12">
-        <f t="shared" ref="L38:L69" si="11">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
         <v>7.5999999999993406E-2</v>
       </c>
       <c r="M38" s="12"/>
@@ -5045,7 +5144,7 @@
       <c r="P38" s="12"/>
       <c r="Q38" s="12"/>
       <c r="R38" s="12">
-        <f t="shared" ref="R38:R69" si="12">E38/5</f>
+        <f t="shared" ref="R38:R69" si="13">E38/5</f>
         <v>15.555199999999999</v>
       </c>
       <c r="S38" s="4">
@@ -5061,7 +5160,7 @@
         <v>8</v>
       </c>
       <c r="V38" s="12">
-        <f t="shared" ref="V38:V69" si="13">(F38+O38+P38+Q38)/R38</f>
+        <f t="shared" ref="V38:V69" si="14">(F38+O38+P38+Q38)/R38</f>
         <v>2.239829767537544</v>
       </c>
       <c r="W38" s="12">
@@ -5099,7 +5198,10 @@
         <f t="shared" si="7"/>
         <v>90</v>
       </c>
-      <c r="AI38" s="12"/>
+      <c r="AI38" s="12">
+        <f t="shared" si="8"/>
+        <v>15.555199999999999</v>
+      </c>
       <c r="AJ38" s="12"/>
       <c r="AK38" s="12"/>
       <c r="AL38" s="12"/>
@@ -5146,7 +5248,7 @@
         <v>99</v>
       </c>
       <c r="L39" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-5</v>
       </c>
       <c r="M39" s="12"/>
@@ -5157,11 +5259,11 @@
       <c r="P39" s="12"/>
       <c r="Q39" s="12"/>
       <c r="R39" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>18.8</v>
       </c>
       <c r="S39" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>33.800000000000011</v>
       </c>
       <c r="T39" s="4">
@@ -5173,7 +5275,7 @@
         <v>11</v>
       </c>
       <c r="V39" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.202127659574467</v>
       </c>
       <c r="W39" s="12">
@@ -5211,7 +5313,10 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="AI39" s="12"/>
+      <c r="AI39" s="12">
+        <f t="shared" si="8"/>
+        <v>1.8800000000000001</v>
+      </c>
       <c r="AJ39" s="12"/>
       <c r="AK39" s="12"/>
       <c r="AL39" s="12"/>
@@ -5252,7 +5357,7 @@
         <v>22</v>
       </c>
       <c r="L40" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-36</v>
       </c>
       <c r="M40" s="12"/>
@@ -5265,7 +5370,7 @@
       </c>
       <c r="Q40" s="12"/>
       <c r="R40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-2.8</v>
       </c>
       <c r="S40" s="4">
@@ -5280,7 +5385,7 @@
         <v>-13.214285714285715</v>
       </c>
       <c r="V40" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.7857142857142858</v>
       </c>
       <c r="W40" s="12">
@@ -5318,7 +5423,10 @@
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="AI40" s="12"/>
+      <c r="AI40" s="12">
+        <f t="shared" si="8"/>
+        <v>-0.97999999999999987</v>
+      </c>
       <c r="AJ40" s="12"/>
       <c r="AK40" s="12"/>
       <c r="AL40" s="12"/>
@@ -5363,7 +5471,7 @@
         <v>89.4</v>
       </c>
       <c r="L41" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-19.359000000000009</v>
       </c>
       <c r="M41" s="12"/>
@@ -5376,7 +5484,7 @@
       </c>
       <c r="Q41" s="12"/>
       <c r="R41" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.008199999999999</v>
       </c>
       <c r="S41" s="4">
@@ -5391,7 +5499,7 @@
         <v>2.3811767393383878</v>
       </c>
       <c r="V41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.23957396382119059</v>
       </c>
       <c r="W41" s="12">
@@ -5429,7 +5537,10 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="AI41" s="12"/>
+      <c r="AI41" s="12">
+        <f t="shared" si="8"/>
+        <v>14.008199999999999</v>
+      </c>
       <c r="AJ41" s="12"/>
       <c r="AK41" s="12"/>
       <c r="AL41" s="12"/>
@@ -5474,7 +5585,7 @@
         <v>21</v>
       </c>
       <c r="L42" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-14</v>
       </c>
       <c r="M42" s="8"/>
@@ -5485,7 +5596,7 @@
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
       <c r="R42" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.4</v>
       </c>
       <c r="S42" s="10"/>
@@ -5498,7 +5609,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="W42" s="8">
@@ -5536,7 +5647,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI42" s="12"/>
+      <c r="AI42" s="12">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AJ42" s="12"/>
       <c r="AK42" s="12"/>
       <c r="AL42" s="12"/>
@@ -5583,7 +5697,7 @@
         <v>275</v>
       </c>
       <c r="L43" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-153</v>
       </c>
       <c r="M43" s="12"/>
@@ -5594,14 +5708,14 @@
       <c r="P43" s="12"/>
       <c r="Q43" s="12"/>
       <c r="R43" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>24.4</v>
       </c>
       <c r="S43" s="4">
         <v>100</v>
       </c>
       <c r="T43" s="4">
-        <f t="shared" ref="T43:T46" si="14">S43*0.7</f>
+        <f t="shared" ref="T43:T46" si="15">S43*0.7</f>
         <v>70</v>
       </c>
       <c r="U43" s="12">
@@ -5609,7 +5723,7 @@
         <v>6.557377049180328</v>
       </c>
       <c r="V43" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.6885245901639347</v>
       </c>
       <c r="W43" s="12">
@@ -5647,7 +5761,10 @@
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
-      <c r="AI43" s="12"/>
+      <c r="AI43" s="12">
+        <f t="shared" si="8"/>
+        <v>9.76</v>
+      </c>
       <c r="AJ43" s="12"/>
       <c r="AK43" s="12"/>
       <c r="AL43" s="12"/>
@@ -5694,7 +5811,7 @@
         <v>253</v>
       </c>
       <c r="L44" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-49</v>
       </c>
       <c r="M44" s="12"/>
@@ -5705,14 +5822,14 @@
       <c r="P44" s="12"/>
       <c r="Q44" s="12"/>
       <c r="R44" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>40.799999999999997</v>
       </c>
       <c r="S44" s="4">
         <v>120</v>
       </c>
       <c r="T44" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>84</v>
       </c>
       <c r="U44" s="12">
@@ -5720,7 +5837,7 @@
         <v>7.916666666666667</v>
       </c>
       <c r="V44" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.8578431372549025</v>
       </c>
       <c r="W44" s="12">
@@ -5758,7 +5875,10 @@
         <f t="shared" si="7"/>
         <v>34</v>
       </c>
-      <c r="AI44" s="12"/>
+      <c r="AI44" s="12">
+        <f t="shared" si="8"/>
+        <v>16.32</v>
+      </c>
       <c r="AJ44" s="12"/>
       <c r="AK44" s="12"/>
       <c r="AL44" s="12"/>
@@ -5803,7 +5923,7 @@
         <v>83.6</v>
       </c>
       <c r="L45" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-29.755999999999993</v>
       </c>
       <c r="M45" s="12"/>
@@ -5816,14 +5936,14 @@
       </c>
       <c r="Q45" s="12"/>
       <c r="R45" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10.768800000000001</v>
       </c>
       <c r="S45" s="4">
         <v>60</v>
       </c>
       <c r="T45" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>42</v>
       </c>
       <c r="U45" s="12">
@@ -5831,7 +5951,7 @@
         <v>3.005348785379987</v>
       </c>
       <c r="V45" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-0.89480722086026288</v>
       </c>
       <c r="W45" s="12">
@@ -5869,7 +5989,10 @@
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
-      <c r="AI45" s="12"/>
+      <c r="AI45" s="12">
+        <f t="shared" si="8"/>
+        <v>10.768800000000001</v>
+      </c>
       <c r="AJ45" s="12"/>
       <c r="AK45" s="12"/>
       <c r="AL45" s="12"/>
@@ -5916,7 +6039,7 @@
         <v>305</v>
       </c>
       <c r="L46" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-82</v>
       </c>
       <c r="M46" s="12"/>
@@ -5929,14 +6052,14 @@
       </c>
       <c r="Q46" s="12"/>
       <c r="R46" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>44.6</v>
       </c>
       <c r="S46" s="4">
         <v>150</v>
       </c>
       <c r="T46" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>105</v>
       </c>
       <c r="U46" s="12">
@@ -5944,7 +6067,7 @@
         <v>2.0179372197309418</v>
       </c>
       <c r="V46" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-0.33632286995515709</v>
       </c>
       <c r="W46" s="12">
@@ -5982,7 +6105,10 @@
         <f t="shared" si="7"/>
         <v>37</v>
       </c>
-      <c r="AI46" s="12"/>
+      <c r="AI46" s="12">
+        <f t="shared" si="8"/>
+        <v>15.61</v>
+      </c>
       <c r="AJ46" s="12"/>
       <c r="AK46" s="12"/>
       <c r="AL46" s="12"/>
@@ -6029,7 +6155,7 @@
         <v>433</v>
       </c>
       <c r="L47" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-61</v>
       </c>
       <c r="M47" s="12"/>
@@ -6040,11 +6166,11 @@
       <c r="P47" s="12"/>
       <c r="Q47" s="12"/>
       <c r="R47" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>74.400000000000006</v>
       </c>
       <c r="S47" s="4">
-        <f t="shared" ref="S47:S64" si="15">11*R47-Q47-P47-O47-F47</f>
+        <f t="shared" ref="S47:S64" si="16">11*R47-Q47-P47-O47-F47</f>
         <v>422.976</v>
       </c>
       <c r="T47" s="4">
@@ -6056,7 +6182,7 @@
         <v>11</v>
       </c>
       <c r="V47" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.3148387096774199</v>
       </c>
       <c r="W47" s="12">
@@ -6094,7 +6220,10 @@
         <f t="shared" si="7"/>
         <v>169</v>
       </c>
-      <c r="AI47" s="12"/>
+      <c r="AI47" s="12">
+        <f t="shared" si="8"/>
+        <v>29.760000000000005</v>
+      </c>
       <c r="AJ47" s="12"/>
       <c r="AK47" s="12"/>
       <c r="AL47" s="12"/>
@@ -6141,7 +6270,7 @@
         <v>66.900000000000006</v>
       </c>
       <c r="L48" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.4190000000000111</v>
       </c>
       <c r="M48" s="12"/>
@@ -6152,7 +6281,7 @@
       <c r="P48" s="12"/>
       <c r="Q48" s="12"/>
       <c r="R48" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13.0962</v>
       </c>
       <c r="S48" s="4"/>
@@ -6165,7 +6294,7 @@
         <v>12.150587804095844</v>
       </c>
       <c r="V48" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12.150587804095844</v>
       </c>
       <c r="W48" s="12">
@@ -6203,7 +6332,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI48" s="12"/>
+      <c r="AI48" s="12">
+        <f t="shared" si="8"/>
+        <v>13.0962</v>
+      </c>
       <c r="AJ48" s="12"/>
       <c r="AK48" s="12"/>
       <c r="AL48" s="12"/>
@@ -6250,7 +6382,7 @@
         <v>174.9</v>
       </c>
       <c r="L49" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-147.99299999999999</v>
       </c>
       <c r="M49" s="12"/>
@@ -6261,7 +6393,7 @@
       <c r="P49" s="12"/>
       <c r="Q49" s="12"/>
       <c r="R49" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.3814000000000002</v>
       </c>
       <c r="S49" s="4"/>
@@ -6274,7 +6406,7 @@
         <v>15.496896718326084</v>
       </c>
       <c r="V49" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>15.496896718326084</v>
       </c>
       <c r="W49" s="12">
@@ -6314,7 +6446,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI49" s="12"/>
+      <c r="AI49" s="12">
+        <f t="shared" si="8"/>
+        <v>5.3814000000000002</v>
+      </c>
       <c r="AJ49" s="12"/>
       <c r="AK49" s="12"/>
       <c r="AL49" s="12"/>
@@ -6359,7 +6494,7 @@
         <v>41.2</v>
       </c>
       <c r="L50" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-49.869</v>
       </c>
       <c r="M50" s="12"/>
@@ -6372,7 +6507,7 @@
       </c>
       <c r="Q50" s="12"/>
       <c r="R50" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.7338</v>
       </c>
       <c r="S50" s="4">
@@ -6387,7 +6522,7 @@
         <v>-48.698811858345827</v>
       </c>
       <c r="V50" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-0.2503172222863061</v>
       </c>
       <c r="W50" s="12">
@@ -6425,7 +6560,10 @@
         <f t="shared" si="7"/>
         <v>84</v>
       </c>
-      <c r="AI50" s="12"/>
+      <c r="AI50" s="12">
+        <f t="shared" si="8"/>
+        <v>-1.7338</v>
+      </c>
       <c r="AJ50" s="12"/>
       <c r="AK50" s="12"/>
       <c r="AL50" s="12"/>
@@ -6472,7 +6610,7 @@
         <v>166</v>
       </c>
       <c r="L51" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4</v>
       </c>
       <c r="M51" s="12"/>
@@ -6483,11 +6621,11 @@
       <c r="P51" s="12"/>
       <c r="Q51" s="12"/>
       <c r="R51" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>32.4</v>
       </c>
       <c r="S51" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>137.61999999999998</v>
       </c>
       <c r="T51" s="4">
@@ -6499,7 +6637,7 @@
         <v>11</v>
       </c>
       <c r="V51" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.7524691358024693</v>
       </c>
       <c r="W51" s="12">
@@ -6537,7 +6675,10 @@
         <f t="shared" si="7"/>
         <v>62</v>
       </c>
-      <c r="AI51" s="12"/>
+      <c r="AI51" s="12">
+        <f t="shared" si="8"/>
+        <v>14.58</v>
+      </c>
       <c r="AJ51" s="12"/>
       <c r="AK51" s="12"/>
       <c r="AL51" s="12"/>
@@ -6584,7 +6725,7 @@
         <v>231</v>
       </c>
       <c r="L52" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-35</v>
       </c>
       <c r="M52" s="12"/>
@@ -6595,11 +6736,11 @@
       <c r="P52" s="12"/>
       <c r="Q52" s="12"/>
       <c r="R52" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>39.200000000000003</v>
       </c>
       <c r="S52" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>76.384000000000071</v>
       </c>
       <c r="T52" s="4">
@@ -6611,7 +6752,7 @@
         <v>11</v>
       </c>
       <c r="V52" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.0514285714285698</v>
       </c>
       <c r="W52" s="12">
@@ -6649,7 +6790,10 @@
         <f t="shared" si="7"/>
         <v>34</v>
       </c>
-      <c r="AI52" s="12"/>
+      <c r="AI52" s="12">
+        <f t="shared" si="8"/>
+        <v>17.64</v>
+      </c>
       <c r="AJ52" s="12"/>
       <c r="AK52" s="12"/>
       <c r="AL52" s="12"/>
@@ -6696,7 +6840,7 @@
         <v>85</v>
       </c>
       <c r="L53" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-3</v>
       </c>
       <c r="M53" s="12"/>
@@ -6707,14 +6851,14 @@
       <c r="P53" s="12"/>
       <c r="Q53" s="12"/>
       <c r="R53" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>16.399999999999999</v>
       </c>
       <c r="S53" s="4">
         <v>50</v>
       </c>
       <c r="T53" s="4">
-        <f t="shared" ref="T53:T54" si="16">S53*0.7</f>
+        <f t="shared" ref="T53:T54" si="17">S53*0.7</f>
         <v>35</v>
       </c>
       <c r="U53" s="12">
@@ -6722,7 +6866,7 @@
         <v>4.51219512195122</v>
       </c>
       <c r="V53" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.3780487804878052</v>
       </c>
       <c r="W53" s="12">
@@ -6760,7 +6904,10 @@
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
-      <c r="AI53" s="12"/>
+      <c r="AI53" s="12">
+        <f t="shared" si="8"/>
+        <v>6.56</v>
+      </c>
       <c r="AJ53" s="12"/>
       <c r="AK53" s="12"/>
       <c r="AL53" s="12"/>
@@ -6807,7 +6954,7 @@
         <v>66</v>
       </c>
       <c r="L54" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4</v>
       </c>
       <c r="M54" s="12"/>
@@ -6818,14 +6965,14 @@
       <c r="P54" s="12"/>
       <c r="Q54" s="12"/>
       <c r="R54" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12.4</v>
       </c>
       <c r="S54" s="4">
         <v>50</v>
       </c>
       <c r="T54" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>35</v>
       </c>
       <c r="U54" s="12">
@@ -6833,7 +6980,7 @@
         <v>6.524193548387097</v>
       </c>
       <c r="V54" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.7016129032258069</v>
       </c>
       <c r="W54" s="12">
@@ -6871,7 +7018,10 @@
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
-      <c r="AI54" s="12"/>
+      <c r="AI54" s="12">
+        <f t="shared" si="8"/>
+        <v>4.9600000000000009</v>
+      </c>
       <c r="AJ54" s="12"/>
       <c r="AK54" s="12"/>
       <c r="AL54" s="12"/>
@@ -6918,7 +7068,7 @@
         <v>62.9</v>
       </c>
       <c r="L55" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-22.056999999999995</v>
       </c>
       <c r="M55" s="12"/>
@@ -6929,7 +7079,7 @@
       <c r="P55" s="12"/>
       <c r="Q55" s="12"/>
       <c r="R55" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8.1686000000000014</v>
       </c>
       <c r="S55" s="4"/>
@@ -6942,7 +7092,7 @@
         <v>13.708228582621258</v>
       </c>
       <c r="V55" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.708228582621258</v>
       </c>
       <c r="W55" s="12">
@@ -6980,7 +7130,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI55" s="12"/>
+      <c r="AI55" s="12">
+        <f t="shared" si="8"/>
+        <v>8.1686000000000014</v>
+      </c>
       <c r="AJ55" s="12"/>
       <c r="AK55" s="12"/>
       <c r="AL55" s="12"/>
@@ -7027,7 +7180,7 @@
         <v>60</v>
       </c>
       <c r="L56" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-5</v>
       </c>
       <c r="M56" s="12"/>
@@ -7038,7 +7191,7 @@
       <c r="P56" s="12"/>
       <c r="Q56" s="12"/>
       <c r="R56" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11</v>
       </c>
       <c r="S56" s="4"/>
@@ -7051,7 +7204,7 @@
         <v>19.90909090909091</v>
       </c>
       <c r="V56" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>19.90909090909091</v>
       </c>
       <c r="W56" s="12">
@@ -7091,7 +7244,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI56" s="12"/>
+      <c r="AI56" s="12">
+        <f t="shared" si="8"/>
+        <v>1.1000000000000001</v>
+      </c>
       <c r="AJ56" s="12"/>
       <c r="AK56" s="12"/>
       <c r="AL56" s="12"/>
@@ -7138,7 +7294,7 @@
         <v>109.8</v>
       </c>
       <c r="L57" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-50.537999999999997</v>
       </c>
       <c r="M57" s="12"/>
@@ -7149,7 +7305,7 @@
       <c r="P57" s="12"/>
       <c r="Q57" s="12"/>
       <c r="R57" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11.852399999999999</v>
       </c>
       <c r="S57" s="4"/>
@@ -7162,7 +7318,7 @@
         <v>18.773765988323042</v>
       </c>
       <c r="V57" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>18.773765988323042</v>
       </c>
       <c r="W57" s="12">
@@ -7200,7 +7356,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI57" s="12"/>
+      <c r="AI57" s="12">
+        <f t="shared" si="8"/>
+        <v>11.852399999999999</v>
+      </c>
       <c r="AJ57" s="12"/>
       <c r="AK57" s="12"/>
       <c r="AL57" s="12"/>
@@ -7247,7 +7406,7 @@
         <v>35.5</v>
       </c>
       <c r="L58" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.32099999999999795</v>
       </c>
       <c r="M58" s="12"/>
@@ -7258,11 +7417,11 @@
       <c r="P58" s="12"/>
       <c r="Q58" s="12"/>
       <c r="R58" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.0358000000000001</v>
       </c>
       <c r="S58" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14.319399999999995</v>
       </c>
       <c r="T58" s="4">
@@ -7274,7 +7433,7 @@
         <v>11</v>
       </c>
       <c r="V58" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.9647801245060972</v>
       </c>
       <c r="W58" s="12">
@@ -7312,7 +7471,10 @@
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
-      <c r="AI58" s="12"/>
+      <c r="AI58" s="12">
+        <f t="shared" si="8"/>
+        <v>7.0358000000000001</v>
+      </c>
       <c r="AJ58" s="12"/>
       <c r="AK58" s="12"/>
       <c r="AL58" s="12"/>
@@ -7357,7 +7519,7 @@
         <v>81</v>
       </c>
       <c r="L59" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M59" s="12"/>
@@ -7368,11 +7530,11 @@
       <c r="P59" s="12"/>
       <c r="Q59" s="12"/>
       <c r="R59" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>16.2</v>
       </c>
       <c r="S59" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>55.199999999999989</v>
       </c>
       <c r="T59" s="4">
@@ -7384,7 +7546,7 @@
         <v>11</v>
       </c>
       <c r="V59" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.5925925925925926</v>
       </c>
       <c r="W59" s="12">
@@ -7422,7 +7584,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="AI59" s="12"/>
+      <c r="AI59" s="12">
+        <f t="shared" si="8"/>
+        <v>1.62</v>
+      </c>
       <c r="AJ59" s="12"/>
       <c r="AK59" s="12"/>
       <c r="AL59" s="12"/>
@@ -7467,7 +7632,7 @@
         <v>30</v>
       </c>
       <c r="L60" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-13</v>
       </c>
       <c r="M60" s="12"/>
@@ -7478,7 +7643,7 @@
       <c r="P60" s="12"/>
       <c r="Q60" s="12"/>
       <c r="R60" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.4</v>
       </c>
       <c r="S60" s="4">
@@ -7494,7 +7659,7 @@
         <v>9</v>
       </c>
       <c r="V60" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.8235294117647065</v>
       </c>
       <c r="W60" s="12">
@@ -7532,7 +7697,10 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="AI60" s="12"/>
+      <c r="AI60" s="12">
+        <f t="shared" si="8"/>
+        <v>1.36</v>
+      </c>
       <c r="AJ60" s="12"/>
       <c r="AK60" s="12"/>
       <c r="AL60" s="12"/>
@@ -7579,7 +7747,7 @@
         <v>205</v>
       </c>
       <c r="L61" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.85900000000000887</v>
       </c>
       <c r="M61" s="12"/>
@@ -7590,7 +7758,7 @@
       <c r="P61" s="12"/>
       <c r="Q61" s="12"/>
       <c r="R61" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>41.171800000000005</v>
       </c>
       <c r="S61" s="4">
@@ -7605,7 +7773,7 @@
         <v>3.505409042111348</v>
       </c>
       <c r="V61" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.95511976644207919</v>
       </c>
       <c r="W61" s="12">
@@ -7643,7 +7811,10 @@
         <f t="shared" si="7"/>
         <v>105</v>
       </c>
-      <c r="AI61" s="12"/>
+      <c r="AI61" s="12">
+        <f t="shared" si="8"/>
+        <v>41.171800000000005</v>
+      </c>
       <c r="AJ61" s="12"/>
       <c r="AK61" s="12"/>
       <c r="AL61" s="12"/>
@@ -7690,7 +7861,7 @@
         <v>155.9</v>
       </c>
       <c r="L62" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-11.992000000000019</v>
       </c>
       <c r="M62" s="12"/>
@@ -7701,7 +7872,7 @@
       <c r="P62" s="12"/>
       <c r="Q62" s="12"/>
       <c r="R62" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>28.781599999999997</v>
       </c>
       <c r="S62" s="4">
@@ -7717,7 +7888,7 @@
         <v>8</v>
       </c>
       <c r="V62" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.0068498624120958</v>
       </c>
       <c r="W62" s="12">
@@ -7757,7 +7928,10 @@
         <f t="shared" si="7"/>
         <v>172</v>
       </c>
-      <c r="AI62" s="12"/>
+      <c r="AI62" s="12">
+        <f t="shared" si="8"/>
+        <v>28.781599999999997</v>
+      </c>
       <c r="AJ62" s="12"/>
       <c r="AK62" s="12"/>
       <c r="AL62" s="12"/>
@@ -7804,7 +7978,7 @@
         <v>784</v>
       </c>
       <c r="L63" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-397</v>
       </c>
       <c r="M63" s="12"/>
@@ -7815,7 +7989,7 @@
       <c r="P63" s="12"/>
       <c r="Q63" s="12"/>
       <c r="R63" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>77.400000000000006</v>
       </c>
       <c r="S63" s="4"/>
@@ -7828,7 +8002,7 @@
         <v>11.569793281653745</v>
       </c>
       <c r="V63" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>11.569793281653745</v>
       </c>
       <c r="W63" s="12">
@@ -7866,7 +8040,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI63" s="12"/>
+      <c r="AI63" s="12">
+        <f t="shared" si="8"/>
+        <v>30.960000000000004</v>
+      </c>
       <c r="AJ63" s="12"/>
       <c r="AK63" s="12"/>
       <c r="AL63" s="12"/>
@@ -7913,7 +8090,7 @@
         <v>366</v>
       </c>
       <c r="L64" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-125</v>
       </c>
       <c r="M64" s="12"/>
@@ -7924,15 +8101,15 @@
       <c r="P64" s="12"/>
       <c r="Q64" s="12"/>
       <c r="R64" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>48.2</v>
       </c>
       <c r="S64" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>169.42000000000002</v>
       </c>
       <c r="T64" s="4">
-        <f t="shared" ref="T64:T68" si="17">S64*0.7</f>
+        <f t="shared" ref="T64:T68" si="18">S64*0.7</f>
         <v>118.59400000000001</v>
       </c>
       <c r="U64" s="12">
@@ -7940,7 +8117,7 @@
         <v>9.9455186721991709</v>
       </c>
       <c r="V64" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.4850622406639005</v>
       </c>
       <c r="W64" s="12">
@@ -7978,7 +8155,10 @@
         <f t="shared" si="7"/>
         <v>47</v>
       </c>
-      <c r="AI64" s="12"/>
+      <c r="AI64" s="12">
+        <f t="shared" si="8"/>
+        <v>19.28</v>
+      </c>
       <c r="AJ64" s="12"/>
       <c r="AK64" s="12"/>
       <c r="AL64" s="12"/>
@@ -8025,7 +8205,7 @@
         <v>95.4</v>
       </c>
       <c r="L65" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-20.707000000000008</v>
       </c>
       <c r="M65" s="12"/>
@@ -8038,14 +8218,14 @@
       </c>
       <c r="Q65" s="12"/>
       <c r="R65" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.938599999999999</v>
       </c>
       <c r="S65" s="4">
         <v>100</v>
       </c>
       <c r="T65" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>70</v>
       </c>
       <c r="U65" s="12">
@@ -8053,7 +8233,7 @@
         <v>11.722101669500491</v>
       </c>
       <c r="V65" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.0362542674681716</v>
       </c>
       <c r="W65" s="12">
@@ -8091,7 +8271,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AI65" s="12"/>
+      <c r="AI65" s="12">
+        <f t="shared" si="8"/>
+        <v>14.938599999999999</v>
+      </c>
       <c r="AJ65" s="12"/>
       <c r="AK65" s="12"/>
       <c r="AL65" s="12"/>
@@ -8138,7 +8321,7 @@
         <v>147.69999999999999</v>
       </c>
       <c r="L66" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-86.185999999999979</v>
       </c>
       <c r="M66" s="12"/>
@@ -8151,14 +8334,14 @@
       </c>
       <c r="Q66" s="12"/>
       <c r="R66" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12.302800000000001</v>
       </c>
       <c r="S66" s="4">
         <v>70</v>
       </c>
       <c r="T66" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>49</v>
       </c>
       <c r="U66" s="12">
@@ -8166,7 +8349,7 @@
         <v>7.4879053548785626</v>
       </c>
       <c r="V66" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.5050721786910284</v>
       </c>
       <c r="W66" s="12">
@@ -8204,7 +8387,10 @@
         <f t="shared" si="7"/>
         <v>49</v>
       </c>
-      <c r="AI66" s="12"/>
+      <c r="AI66" s="12">
+        <f t="shared" si="8"/>
+        <v>12.302800000000001</v>
+      </c>
       <c r="AJ66" s="12"/>
       <c r="AK66" s="12"/>
       <c r="AL66" s="12"/>
@@ -8251,7 +8437,7 @@
         <v>473</v>
       </c>
       <c r="L67" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>19.488999999999976</v>
       </c>
       <c r="M67" s="12"/>
@@ -8262,14 +8448,14 @@
       <c r="P67" s="12"/>
       <c r="Q67" s="12"/>
       <c r="R67" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>98.497799999999998</v>
       </c>
       <c r="S67" s="4">
         <v>400</v>
       </c>
       <c r="T67" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>280</v>
       </c>
       <c r="U67" s="12">
@@ -8277,7 +8463,7 @@
         <v>6.3413802135682227</v>
       </c>
       <c r="V67" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.4986771278140227</v>
       </c>
       <c r="W67" s="12">
@@ -8315,7 +8501,10 @@
         <f t="shared" si="7"/>
         <v>280</v>
       </c>
-      <c r="AI67" s="12"/>
+      <c r="AI67" s="12">
+        <f t="shared" si="8"/>
+        <v>98.497799999999998</v>
+      </c>
       <c r="AJ67" s="12"/>
       <c r="AK67" s="12"/>
       <c r="AL67" s="12"/>
@@ -8362,7 +8551,7 @@
         <v>259.51600000000002</v>
       </c>
       <c r="L68" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-159.79300000000001</v>
       </c>
       <c r="M68" s="12"/>
@@ -8375,14 +8564,14 @@
       </c>
       <c r="Q68" s="12"/>
       <c r="R68" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>19.944600000000001</v>
       </c>
       <c r="S68" s="4">
         <v>100</v>
       </c>
       <c r="T68" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>70</v>
       </c>
       <c r="U68" s="12">
@@ -8390,7 +8579,7 @@
         <v>12.447790680184102</v>
       </c>
       <c r="V68" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.938068750438708</v>
       </c>
       <c r="W68" s="12">
@@ -8428,7 +8617,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AI68" s="12"/>
+      <c r="AI68" s="12">
+        <f t="shared" si="8"/>
+        <v>19.944600000000001</v>
+      </c>
       <c r="AJ68" s="12"/>
       <c r="AK68" s="12"/>
       <c r="AL68" s="12"/>
@@ -8463,7 +8655,7 @@
       <c r="J69" s="8"/>
       <c r="K69" s="8"/>
       <c r="L69" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M69" s="8"/>
@@ -8474,7 +8666,7 @@
       <c r="P69" s="8"/>
       <c r="Q69" s="8"/>
       <c r="R69" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S69" s="10"/>
@@ -8487,7 +8679,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="V69" s="8" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W69" s="8">
@@ -8527,7 +8719,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI69" s="12"/>
+      <c r="AI69" s="12">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AJ69" s="12"/>
       <c r="AK69" s="12"/>
       <c r="AL69" s="12"/>
@@ -8574,7 +8769,7 @@
         <v>209.358</v>
       </c>
       <c r="L70" s="12">
-        <f t="shared" ref="L70:L101" si="18">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="19">E70-K70</f>
         <v>-42.908999999999992</v>
       </c>
       <c r="M70" s="12"/>
@@ -8585,7 +8780,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
       <c r="R70" s="12">
-        <f t="shared" ref="R70:R101" si="19">E70/5</f>
+        <f t="shared" ref="R70:R101" si="20">E70/5</f>
         <v>33.2898</v>
       </c>
       <c r="S70" s="4">
@@ -8601,7 +8796,7 @@
         <v>10</v>
       </c>
       <c r="V70" s="12">
-        <f t="shared" ref="V70:V101" si="20">(F70+O70+P70+Q70)/R70</f>
+        <f t="shared" ref="V70:V101" si="21">(F70+O70+P70+Q70)/R70</f>
         <v>3.8592001153506481</v>
       </c>
       <c r="W70" s="12">
@@ -8639,7 +8834,10 @@
         <f t="shared" si="7"/>
         <v>204</v>
       </c>
-      <c r="AI70" s="12"/>
+      <c r="AI70" s="12">
+        <f t="shared" si="8"/>
+        <v>33.2898</v>
+      </c>
       <c r="AJ70" s="12"/>
       <c r="AK70" s="12"/>
       <c r="AL70" s="12"/>
@@ -8686,7 +8884,7 @@
         <v>87</v>
       </c>
       <c r="L71" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="M71" s="12"/>
@@ -8697,20 +8895,20 @@
       <c r="P71" s="12"/>
       <c r="Q71" s="12"/>
       <c r="R71" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>18.600000000000001</v>
       </c>
       <c r="S71" s="4"/>
       <c r="T71" s="4">
-        <f t="shared" ref="T71:T129" si="21">S71</f>
+        <f t="shared" ref="T71:T129" si="22">S71</f>
         <v>0</v>
       </c>
       <c r="U71" s="12">
-        <f t="shared" ref="U71:U129" si="22">(F71+O71+P71+Q71+T71)/R71</f>
+        <f t="shared" ref="U71:U129" si="23">(F71+O71+P71+Q71+T71)/R71</f>
         <v>12.348387096774196</v>
       </c>
       <c r="V71" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>12.348387096774196</v>
       </c>
       <c r="W71" s="12">
@@ -8745,10 +8943,13 @@
       </c>
       <c r="AG71" s="12"/>
       <c r="AH71" s="12">
-        <f t="shared" ref="AH71:AH129" si="23">ROUND(G71*T71,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI71" s="12"/>
+        <f t="shared" ref="AH71:AH129" si="24">ROUND(G71*T71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI71" s="12">
+        <f t="shared" ref="AI71:AI129" si="25">R71*G71</f>
+        <v>11.16</v>
+      </c>
       <c r="AJ71" s="12"/>
       <c r="AK71" s="12"/>
       <c r="AL71" s="12"/>
@@ -8795,7 +8996,7 @@
         <v>150</v>
       </c>
       <c r="L72" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10</v>
       </c>
       <c r="M72" s="12"/>
@@ -8806,23 +9007,23 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
       <c r="R72" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>32</v>
       </c>
       <c r="S72" s="4">
-        <f t="shared" ref="S72:S75" si="24">11*R72-Q72-P72-O72-F72</f>
+        <f t="shared" ref="S72:S75" si="26">11*R72-Q72-P72-O72-F72</f>
         <v>74.124000000000024</v>
       </c>
       <c r="T72" s="4">
+        <f t="shared" si="22"/>
+        <v>74.124000000000024</v>
+      </c>
+      <c r="U72" s="12">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="V72" s="12">
         <f t="shared" si="21"/>
-        <v>74.124000000000024</v>
-      </c>
-      <c r="U72" s="12">
-        <f t="shared" si="22"/>
-        <v>11</v>
-      </c>
-      <c r="V72" s="12">
-        <f t="shared" si="20"/>
         <v>8.6836249999999993</v>
       </c>
       <c r="W72" s="12">
@@ -8857,10 +9058,13 @@
       </c>
       <c r="AG72" s="12"/>
       <c r="AH72" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>44</v>
       </c>
-      <c r="AI72" s="12"/>
+      <c r="AI72" s="12">
+        <f t="shared" si="25"/>
+        <v>19.2</v>
+      </c>
       <c r="AJ72" s="12"/>
       <c r="AK72" s="12"/>
       <c r="AL72" s="12"/>
@@ -8907,7 +9111,7 @@
         <v>128</v>
       </c>
       <c r="L73" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-2</v>
       </c>
       <c r="M73" s="12"/>
@@ -8918,23 +9122,23 @@
       <c r="P73" s="12"/>
       <c r="Q73" s="12"/>
       <c r="R73" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>25.2</v>
       </c>
       <c r="S73" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>81.22799999999998</v>
       </c>
       <c r="T73" s="4">
+        <f t="shared" si="22"/>
+        <v>81.22799999999998</v>
+      </c>
+      <c r="U73" s="12">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="V73" s="12">
         <f t="shared" si="21"/>
-        <v>81.22799999999998</v>
-      </c>
-      <c r="U73" s="12">
-        <f t="shared" si="22"/>
-        <v>11</v>
-      </c>
-      <c r="V73" s="12">
-        <f t="shared" si="20"/>
         <v>7.7766666666666673</v>
       </c>
       <c r="W73" s="12">
@@ -8969,10 +9173,13 @@
       </c>
       <c r="AG73" s="12"/>
       <c r="AH73" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>32</v>
       </c>
-      <c r="AI73" s="12"/>
+      <c r="AI73" s="12">
+        <f t="shared" si="25"/>
+        <v>10.08</v>
+      </c>
       <c r="AJ73" s="12"/>
       <c r="AK73" s="12"/>
       <c r="AL73" s="12"/>
@@ -9019,7 +9226,7 @@
         <v>261</v>
       </c>
       <c r="L74" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-8</v>
       </c>
       <c r="M74" s="12"/>
@@ -9030,23 +9237,23 @@
       <c r="P74" s="12"/>
       <c r="Q74" s="12"/>
       <c r="R74" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>50.6</v>
       </c>
       <c r="S74" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>268.87400000000002</v>
       </c>
       <c r="T74" s="4">
+        <f t="shared" si="22"/>
+        <v>268.87400000000002</v>
+      </c>
+      <c r="U74" s="12">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="V74" s="12">
         <f t="shared" si="21"/>
-        <v>268.87400000000002</v>
-      </c>
-      <c r="U74" s="12">
-        <f t="shared" si="22"/>
-        <v>11</v>
-      </c>
-      <c r="V74" s="12">
-        <f t="shared" si="20"/>
         <v>5.6862845849802373</v>
       </c>
       <c r="W74" s="12">
@@ -9081,10 +9288,13 @@
       </c>
       <c r="AG74" s="12"/>
       <c r="AH74" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>89</v>
       </c>
-      <c r="AI74" s="12"/>
+      <c r="AI74" s="12">
+        <f t="shared" si="25"/>
+        <v>16.698</v>
+      </c>
       <c r="AJ74" s="12"/>
       <c r="AK74" s="12"/>
       <c r="AL74" s="12"/>
@@ -9131,7 +9341,7 @@
         <v>149</v>
       </c>
       <c r="L75" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M75" s="12"/>
@@ -9142,23 +9352,23 @@
       <c r="P75" s="12"/>
       <c r="Q75" s="12"/>
       <c r="R75" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>29.8</v>
       </c>
       <c r="S75" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>120.8880000000002</v>
       </c>
       <c r="T75" s="4">
+        <f t="shared" si="22"/>
+        <v>120.8880000000002</v>
+      </c>
+      <c r="U75" s="12">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="V75" s="12">
         <f t="shared" si="21"/>
-        <v>120.8880000000002</v>
-      </c>
-      <c r="U75" s="12">
-        <f t="shared" si="22"/>
-        <v>11</v>
-      </c>
-      <c r="V75" s="12">
-        <f t="shared" si="20"/>
         <v>6.9433557046979804</v>
       </c>
       <c r="W75" s="12">
@@ -9193,10 +9403,13 @@
       </c>
       <c r="AG75" s="12"/>
       <c r="AH75" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>42</v>
       </c>
-      <c r="AI75" s="12"/>
+      <c r="AI75" s="12">
+        <f t="shared" si="25"/>
+        <v>10.43</v>
+      </c>
       <c r="AJ75" s="12"/>
       <c r="AK75" s="12"/>
       <c r="AL75" s="12"/>
@@ -9231,7 +9444,7 @@
       <c r="J76" s="8"/>
       <c r="K76" s="8"/>
       <c r="L76" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M76" s="8"/>
@@ -9242,20 +9455,20 @@
       <c r="P76" s="8"/>
       <c r="Q76" s="8"/>
       <c r="R76" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S76" s="10"/>
       <c r="T76" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U76" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V76" s="8" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U76" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V76" s="8" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W76" s="8">
@@ -9292,10 +9505,13 @@
         <v>44</v>
       </c>
       <c r="AH76" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI76" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI76" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AJ76" s="12"/>
       <c r="AK76" s="12"/>
       <c r="AL76" s="12"/>
@@ -9342,7 +9558,7 @@
         <v>57</v>
       </c>
       <c r="L77" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="M77" s="12"/>
@@ -9353,23 +9569,23 @@
       <c r="P77" s="12"/>
       <c r="Q77" s="12"/>
       <c r="R77" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.8</v>
       </c>
       <c r="S77" s="4">
-        <f t="shared" ref="S77:S79" si="25">11*R77-Q77-P77-O77-F77</f>
+        <f t="shared" ref="S77:S79" si="27">11*R77-Q77-P77-O77-F77</f>
         <v>6.8000000000000114</v>
       </c>
       <c r="T77" s="4">
+        <f t="shared" si="22"/>
+        <v>6.8000000000000114</v>
+      </c>
+      <c r="U77" s="12">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="V77" s="12">
         <f t="shared" si="21"/>
-        <v>6.8000000000000114</v>
-      </c>
-      <c r="U77" s="12">
-        <f t="shared" si="22"/>
-        <v>11</v>
-      </c>
-      <c r="V77" s="12">
-        <f t="shared" si="20"/>
         <v>10.423728813559322</v>
       </c>
       <c r="W77" s="12">
@@ -9404,10 +9620,13 @@
       </c>
       <c r="AG77" s="12"/>
       <c r="AH77" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4</v>
       </c>
-      <c r="AI77" s="12"/>
+      <c r="AI77" s="12">
+        <f t="shared" si="25"/>
+        <v>7.08</v>
+      </c>
       <c r="AJ77" s="12"/>
       <c r="AK77" s="12"/>
       <c r="AL77" s="12"/>
@@ -9454,7 +9673,7 @@
         <v>86</v>
       </c>
       <c r="L78" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-3</v>
       </c>
       <c r="M78" s="12"/>
@@ -9465,7 +9684,7 @@
       <c r="P78" s="12"/>
       <c r="Q78" s="12"/>
       <c r="R78" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>16.600000000000001</v>
       </c>
       <c r="S78" s="4">
@@ -9473,15 +9692,15 @@
         <v>77.800000000000011</v>
       </c>
       <c r="T78" s="4">
+        <f t="shared" si="22"/>
+        <v>77.800000000000011</v>
+      </c>
+      <c r="U78" s="12">
+        <f t="shared" si="23"/>
+        <v>8</v>
+      </c>
+      <c r="V78" s="12">
         <f t="shared" si="21"/>
-        <v>77.800000000000011</v>
-      </c>
-      <c r="U78" s="12">
-        <f t="shared" si="22"/>
-        <v>8</v>
-      </c>
-      <c r="V78" s="12">
-        <f t="shared" si="20"/>
         <v>3.3132530120481927</v>
       </c>
       <c r="W78" s="12">
@@ -9516,10 +9735,13 @@
       </c>
       <c r="AG78" s="12"/>
       <c r="AH78" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>26</v>
       </c>
-      <c r="AI78" s="12"/>
+      <c r="AI78" s="12">
+        <f t="shared" si="25"/>
+        <v>5.4780000000000006</v>
+      </c>
       <c r="AJ78" s="12"/>
       <c r="AK78" s="12"/>
       <c r="AL78" s="12"/>
@@ -9566,7 +9788,7 @@
         <v>63</v>
       </c>
       <c r="L79" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-28</v>
       </c>
       <c r="M79" s="12"/>
@@ -9577,23 +9799,23 @@
       <c r="P79" s="12"/>
       <c r="Q79" s="12"/>
       <c r="R79" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7</v>
       </c>
       <c r="S79" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>22</v>
       </c>
       <c r="T79" s="4">
+        <f t="shared" si="22"/>
+        <v>22</v>
+      </c>
+      <c r="U79" s="12">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="V79" s="12">
         <f t="shared" si="21"/>
-        <v>22</v>
-      </c>
-      <c r="U79" s="12">
-        <f t="shared" si="22"/>
-        <v>11</v>
-      </c>
-      <c r="V79" s="12">
-        <f t="shared" si="20"/>
         <v>7.8571428571428568</v>
       </c>
       <c r="W79" s="12">
@@ -9628,10 +9850,13 @@
       </c>
       <c r="AG79" s="12"/>
       <c r="AH79" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9</v>
       </c>
-      <c r="AI79" s="12"/>
+      <c r="AI79" s="12">
+        <f t="shared" si="25"/>
+        <v>2.8000000000000003</v>
+      </c>
       <c r="AJ79" s="12"/>
       <c r="AK79" s="12"/>
       <c r="AL79" s="12"/>
@@ -9676,7 +9901,7 @@
       <c r="J80" s="12"/>
       <c r="K80" s="12"/>
       <c r="L80" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-2</v>
       </c>
       <c r="M80" s="12"/>
@@ -9687,20 +9912,20 @@
       <c r="P80" s="12"/>
       <c r="Q80" s="12"/>
       <c r="R80" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-0.4</v>
       </c>
       <c r="S80" s="4"/>
       <c r="T80" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U80" s="12">
+        <f t="shared" si="23"/>
+        <v>-52.5</v>
+      </c>
+      <c r="V80" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U80" s="12">
-        <f t="shared" si="22"/>
-        <v>-52.5</v>
-      </c>
-      <c r="V80" s="12">
-        <f t="shared" si="20"/>
         <v>-52.5</v>
       </c>
       <c r="W80" s="12">
@@ -9737,10 +9962,13 @@
         <v>120</v>
       </c>
       <c r="AH80" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI80" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI80" s="12">
+        <f t="shared" si="25"/>
+        <v>-0.13999999999999999</v>
+      </c>
       <c r="AJ80" s="12"/>
       <c r="AK80" s="12"/>
       <c r="AL80" s="12"/>
@@ -9787,7 +10015,7 @@
         <v>65</v>
       </c>
       <c r="L81" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M81" s="12"/>
@@ -9798,20 +10026,20 @@
       <c r="P81" s="12"/>
       <c r="Q81" s="12"/>
       <c r="R81" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>13</v>
       </c>
       <c r="S81" s="4"/>
       <c r="T81" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U81" s="12">
+        <f t="shared" si="23"/>
+        <v>12.358461538461537</v>
+      </c>
+      <c r="V81" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U81" s="12">
-        <f t="shared" si="22"/>
-        <v>12.358461538461537</v>
-      </c>
-      <c r="V81" s="12">
-        <f t="shared" si="20"/>
         <v>12.358461538461537</v>
       </c>
       <c r="W81" s="12">
@@ -9846,10 +10074,13 @@
       </c>
       <c r="AG81" s="12"/>
       <c r="AH81" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI81" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI81" s="12">
+        <f t="shared" si="25"/>
+        <v>4.55</v>
+      </c>
       <c r="AJ81" s="12"/>
       <c r="AK81" s="12"/>
       <c r="AL81" s="12"/>
@@ -9884,7 +10115,7 @@
       <c r="J82" s="8"/>
       <c r="K82" s="8"/>
       <c r="L82" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M82" s="8"/>
@@ -9895,20 +10126,20 @@
       <c r="P82" s="8"/>
       <c r="Q82" s="8"/>
       <c r="R82" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S82" s="10"/>
       <c r="T82" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U82" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V82" s="8" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U82" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V82" s="8" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W82" s="8">
@@ -9945,10 +10176,13 @@
         <v>44</v>
       </c>
       <c r="AH82" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI82" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI82" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AJ82" s="12"/>
       <c r="AK82" s="12"/>
       <c r="AL82" s="12"/>
@@ -9983,7 +10217,7 @@
       <c r="J83" s="8"/>
       <c r="K83" s="8"/>
       <c r="L83" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M83" s="8"/>
@@ -9994,20 +10228,20 @@
       <c r="P83" s="8"/>
       <c r="Q83" s="8"/>
       <c r="R83" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S83" s="10"/>
       <c r="T83" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U83" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V83" s="8" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U83" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V83" s="8" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W83" s="8">
@@ -10044,10 +10278,13 @@
         <v>44</v>
       </c>
       <c r="AH83" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI83" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI83" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AJ83" s="12"/>
       <c r="AK83" s="12"/>
       <c r="AL83" s="12"/>
@@ -10082,7 +10319,7 @@
       <c r="J84" s="8"/>
       <c r="K84" s="8"/>
       <c r="L84" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M84" s="8"/>
@@ -10093,20 +10330,20 @@
       <c r="P84" s="8"/>
       <c r="Q84" s="8"/>
       <c r="R84" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S84" s="10"/>
       <c r="T84" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U84" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V84" s="8" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U84" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V84" s="8" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W84" s="8">
@@ -10143,10 +10380,13 @@
         <v>44</v>
       </c>
       <c r="AH84" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI84" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI84" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AJ84" s="12"/>
       <c r="AK84" s="12"/>
       <c r="AL84" s="12"/>
@@ -10193,7 +10433,7 @@
         <v>188.1</v>
       </c>
       <c r="L85" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-7.1469999999999914</v>
       </c>
       <c r="M85" s="12"/>
@@ -10204,7 +10444,7 @@
       <c r="P85" s="12"/>
       <c r="Q85" s="12"/>
       <c r="R85" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>36.190600000000003</v>
       </c>
       <c r="S85" s="4">
@@ -10212,15 +10452,15 @@
         <v>120.86535400000005</v>
       </c>
       <c r="T85" s="4">
+        <f t="shared" si="22"/>
+        <v>120.86535400000005</v>
+      </c>
+      <c r="U85" s="12">
+        <f t="shared" si="23"/>
+        <v>10.999999999999998</v>
+      </c>
+      <c r="V85" s="12">
         <f t="shared" si="21"/>
-        <v>120.86535400000005</v>
-      </c>
-      <c r="U85" s="12">
-        <f t="shared" si="22"/>
-        <v>10.999999999999998</v>
-      </c>
-      <c r="V85" s="12">
-        <f t="shared" si="20"/>
         <v>7.6603108541997074</v>
       </c>
       <c r="W85" s="12">
@@ -10255,10 +10495,13 @@
       </c>
       <c r="AG85" s="12"/>
       <c r="AH85" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>121</v>
       </c>
-      <c r="AI85" s="12"/>
+      <c r="AI85" s="12">
+        <f t="shared" si="25"/>
+        <v>36.190600000000003</v>
+      </c>
       <c r="AJ85" s="12"/>
       <c r="AK85" s="12"/>
       <c r="AL85" s="12"/>
@@ -10293,7 +10536,7 @@
       <c r="J86" s="8"/>
       <c r="K86" s="8"/>
       <c r="L86" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M86" s="8"/>
@@ -10304,20 +10547,20 @@
       <c r="P86" s="8"/>
       <c r="Q86" s="8"/>
       <c r="R86" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S86" s="10"/>
       <c r="T86" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U86" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V86" s="8" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U86" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V86" s="8" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W86" s="8">
@@ -10354,10 +10597,13 @@
         <v>44</v>
       </c>
       <c r="AH86" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI86" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI86" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AJ86" s="12"/>
       <c r="AK86" s="12"/>
       <c r="AL86" s="12"/>
@@ -10404,7 +10650,7 @@
         <v>1530.954</v>
       </c>
       <c r="L87" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>28.602000000000089</v>
       </c>
       <c r="M87" s="12"/>
@@ -10417,20 +10663,20 @@
         <v>300</v>
       </c>
       <c r="R87" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>311.91120000000001</v>
       </c>
       <c r="S87" s="4"/>
       <c r="T87" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U87" s="12">
+        <f t="shared" si="23"/>
+        <v>9.7875688657540998</v>
+      </c>
+      <c r="V87" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U87" s="12">
-        <f t="shared" si="22"/>
-        <v>9.7875688657540998</v>
-      </c>
-      <c r="V87" s="12">
-        <f t="shared" si="20"/>
         <v>9.7875688657540998</v>
       </c>
       <c r="W87" s="12">
@@ -10465,10 +10711,13 @@
       </c>
       <c r="AG87" s="12"/>
       <c r="AH87" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI87" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI87" s="12">
+        <f t="shared" si="25"/>
+        <v>311.91120000000001</v>
+      </c>
       <c r="AJ87" s="12"/>
       <c r="AK87" s="12"/>
       <c r="AL87" s="12"/>
@@ -10515,7 +10764,7 @@
         <v>854.36500000000001</v>
       </c>
       <c r="L88" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-5.6430000000000291</v>
       </c>
       <c r="M88" s="12"/>
@@ -10528,20 +10777,20 @@
         <v>200</v>
       </c>
       <c r="R88" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>169.74439999999998</v>
       </c>
       <c r="S88" s="4"/>
       <c r="T88" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U88" s="12">
+        <f t="shared" si="23"/>
+        <v>10.778642405876131</v>
+      </c>
+      <c r="V88" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U88" s="12">
-        <f t="shared" si="22"/>
-        <v>10.778642405876131</v>
-      </c>
-      <c r="V88" s="12">
-        <f t="shared" si="20"/>
         <v>10.778642405876131</v>
       </c>
       <c r="W88" s="12">
@@ -10576,10 +10825,13 @@
       </c>
       <c r="AG88" s="12"/>
       <c r="AH88" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI88" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI88" s="12">
+        <f t="shared" si="25"/>
+        <v>169.74439999999998</v>
+      </c>
       <c r="AJ88" s="12"/>
       <c r="AK88" s="12"/>
       <c r="AL88" s="12"/>
@@ -10626,7 +10878,7 @@
         <v>1972.6489999999999</v>
       </c>
       <c r="L89" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-41.421999999999798</v>
       </c>
       <c r="M89" s="12"/>
@@ -10639,20 +10891,20 @@
         <v>400</v>
       </c>
       <c r="R89" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>386.24540000000002</v>
       </c>
       <c r="S89" s="4"/>
       <c r="T89" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U89" s="12">
+        <f t="shared" si="23"/>
+        <v>10.498022521433263</v>
+      </c>
+      <c r="V89" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U89" s="12">
-        <f t="shared" si="22"/>
-        <v>10.498022521433263</v>
-      </c>
-      <c r="V89" s="12">
-        <f t="shared" si="20"/>
         <v>10.498022521433263</v>
       </c>
       <c r="W89" s="12">
@@ -10687,10 +10939,13 @@
       </c>
       <c r="AG89" s="12"/>
       <c r="AH89" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI89" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI89" s="12">
+        <f t="shared" si="25"/>
+        <v>386.24540000000002</v>
+      </c>
       <c r="AJ89" s="12"/>
       <c r="AK89" s="12"/>
       <c r="AL89" s="12"/>
@@ -10725,7 +10980,7 @@
       <c r="J90" s="8"/>
       <c r="K90" s="8"/>
       <c r="L90" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M90" s="8"/>
@@ -10736,20 +10991,20 @@
       <c r="P90" s="8"/>
       <c r="Q90" s="8"/>
       <c r="R90" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S90" s="10"/>
       <c r="T90" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U90" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V90" s="8" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U90" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V90" s="8" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W90" s="8">
@@ -10786,10 +11041,13 @@
         <v>44</v>
       </c>
       <c r="AH90" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI90" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI90" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AJ90" s="12"/>
       <c r="AK90" s="12"/>
       <c r="AL90" s="12"/>
@@ -10836,7 +11094,7 @@
         <v>55</v>
       </c>
       <c r="L91" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-57</v>
       </c>
       <c r="M91" s="12"/>
@@ -10849,7 +11107,7 @@
       </c>
       <c r="Q91" s="12"/>
       <c r="R91" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-0.4</v>
       </c>
       <c r="S91" s="4">
@@ -10860,11 +11118,11 @@
         <v>42</v>
       </c>
       <c r="U91" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-85</v>
       </c>
       <c r="V91" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="W91" s="12">
@@ -10899,10 +11157,13 @@
       </c>
       <c r="AG91" s="12"/>
       <c r="AH91" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>13</v>
       </c>
-      <c r="AI91" s="12"/>
+      <c r="AI91" s="12">
+        <f t="shared" si="25"/>
+        <v>-0.12</v>
+      </c>
       <c r="AJ91" s="12"/>
       <c r="AK91" s="12"/>
       <c r="AL91" s="12"/>
@@ -10937,7 +11198,7 @@
       <c r="J92" s="8"/>
       <c r="K92" s="8"/>
       <c r="L92" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M92" s="8"/>
@@ -10948,20 +11209,20 @@
       <c r="P92" s="8"/>
       <c r="Q92" s="8"/>
       <c r="R92" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S92" s="10"/>
       <c r="T92" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U92" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V92" s="8" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U92" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V92" s="8" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W92" s="8">
@@ -10998,10 +11259,13 @@
         <v>44</v>
       </c>
       <c r="AH92" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI92" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI92" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AJ92" s="12"/>
       <c r="AK92" s="12"/>
       <c r="AL92" s="12"/>
@@ -11048,7 +11312,7 @@
         <v>117</v>
       </c>
       <c r="L93" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-5</v>
       </c>
       <c r="M93" s="12"/>
@@ -11061,22 +11325,22 @@
       </c>
       <c r="Q93" s="12"/>
       <c r="R93" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>22.4</v>
       </c>
       <c r="S93" s="4">
         <v>70</v>
       </c>
       <c r="T93" s="4">
-        <f t="shared" ref="T93:T94" si="26">S93*0.7</f>
+        <f t="shared" ref="T93:T94" si="28">S93*0.7</f>
         <v>49</v>
       </c>
       <c r="U93" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4.1567857142857143</v>
       </c>
       <c r="V93" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.9692857142857141</v>
       </c>
       <c r="W93" s="12">
@@ -11113,10 +11377,13 @@
         <v>134</v>
       </c>
       <c r="AH93" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
-      <c r="AI93" s="12"/>
+      <c r="AI93" s="12">
+        <f t="shared" si="25"/>
+        <v>1.5680000000000001</v>
+      </c>
       <c r="AJ93" s="12"/>
       <c r="AK93" s="12"/>
       <c r="AL93" s="12"/>
@@ -11163,7 +11430,7 @@
         <v>153</v>
       </c>
       <c r="L94" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-85</v>
       </c>
       <c r="M94" s="12"/>
@@ -11174,22 +11441,22 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
       <c r="R94" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>13.6</v>
       </c>
       <c r="S94" s="4">
         <v>80</v>
       </c>
       <c r="T94" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>56</v>
       </c>
       <c r="U94" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6.7647058823529411</v>
       </c>
       <c r="V94" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.6470588235294117</v>
       </c>
       <c r="W94" s="12">
@@ -11226,10 +11493,13 @@
         <v>134</v>
       </c>
       <c r="AH94" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4</v>
       </c>
-      <c r="AI94" s="12"/>
+      <c r="AI94" s="12">
+        <f t="shared" si="25"/>
+        <v>0.95200000000000007</v>
+      </c>
       <c r="AJ94" s="12"/>
       <c r="AK94" s="12"/>
       <c r="AL94" s="12"/>
@@ -11276,7 +11546,7 @@
         <v>89</v>
       </c>
       <c r="L95" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-5</v>
       </c>
       <c r="M95" s="12"/>
@@ -11287,20 +11557,20 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
       <c r="R95" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>16.8</v>
       </c>
       <c r="S95" s="4"/>
       <c r="T95" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U95" s="12">
+        <f t="shared" si="23"/>
+        <v>13.032261904761905</v>
+      </c>
+      <c r="V95" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U95" s="12">
-        <f t="shared" si="22"/>
-        <v>13.032261904761905</v>
-      </c>
-      <c r="V95" s="12">
-        <f t="shared" si="20"/>
         <v>13.032261904761905</v>
       </c>
       <c r="W95" s="12">
@@ -11337,10 +11607,13 @@
         <v>134</v>
       </c>
       <c r="AH95" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI95" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI95" s="12">
+        <f t="shared" si="25"/>
+        <v>1.1760000000000002</v>
+      </c>
       <c r="AJ95" s="12"/>
       <c r="AK95" s="12"/>
       <c r="AL95" s="12"/>
@@ -11387,7 +11660,7 @@
         <v>46</v>
       </c>
       <c r="L96" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-27</v>
       </c>
       <c r="M96" s="8"/>
@@ -11398,20 +11671,20 @@
       <c r="P96" s="8"/>
       <c r="Q96" s="8"/>
       <c r="R96" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.8</v>
       </c>
       <c r="S96" s="10"/>
       <c r="T96" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U96" s="12">
+        <f t="shared" si="23"/>
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="V96" s="8">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U96" s="12">
-        <f t="shared" si="22"/>
-        <v>0.52631578947368418</v>
-      </c>
-      <c r="V96" s="8">
-        <f t="shared" si="20"/>
         <v>0.52631578947368418</v>
       </c>
       <c r="W96" s="8">
@@ -11446,10 +11719,13 @@
       </c>
       <c r="AG96" s="8"/>
       <c r="AH96" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI96" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI96" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AJ96" s="12"/>
       <c r="AK96" s="12"/>
       <c r="AL96" s="12"/>
@@ -11484,7 +11760,7 @@
       <c r="J97" s="8"/>
       <c r="K97" s="8"/>
       <c r="L97" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M97" s="8"/>
@@ -11495,20 +11771,20 @@
       <c r="P97" s="8"/>
       <c r="Q97" s="8"/>
       <c r="R97" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S97" s="10"/>
       <c r="T97" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U97" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V97" s="8" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U97" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V97" s="8" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W97" s="8">
@@ -11545,10 +11821,13 @@
         <v>44</v>
       </c>
       <c r="AH97" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI97" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI97" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AJ97" s="12"/>
       <c r="AK97" s="12"/>
       <c r="AL97" s="12"/>
@@ -11595,7 +11874,7 @@
         <v>5.2</v>
       </c>
       <c r="L98" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-5.78</v>
       </c>
       <c r="M98" s="12"/>
@@ -11606,20 +11885,20 @@
       <c r="P98" s="12"/>
       <c r="Q98" s="12"/>
       <c r="R98" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-0.11599999999999999</v>
       </c>
       <c r="S98" s="4"/>
       <c r="T98" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U98" s="12">
+        <f t="shared" si="23"/>
+        <v>-131.84482758620692</v>
+      </c>
+      <c r="V98" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U98" s="12">
-        <f t="shared" si="22"/>
-        <v>-131.84482758620692</v>
-      </c>
-      <c r="V98" s="12">
-        <f t="shared" si="20"/>
         <v>-131.84482758620692</v>
       </c>
       <c r="W98" s="12">
@@ -11656,10 +11935,13 @@
         <v>176</v>
       </c>
       <c r="AH98" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI98" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI98" s="12">
+        <f t="shared" si="25"/>
+        <v>-0.11599999999999999</v>
+      </c>
       <c r="AJ98" s="12"/>
       <c r="AK98" s="12"/>
       <c r="AL98" s="12"/>
@@ -11704,7 +11986,7 @@
         <v>68</v>
       </c>
       <c r="L99" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-60</v>
       </c>
       <c r="M99" s="12"/>
@@ -11715,20 +11997,20 @@
       <c r="P99" s="12"/>
       <c r="Q99" s="12"/>
       <c r="R99" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.6</v>
       </c>
       <c r="S99" s="4"/>
       <c r="T99" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U99" s="12">
+        <f t="shared" si="23"/>
+        <v>76.111249999999998</v>
+      </c>
+      <c r="V99" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U99" s="12">
-        <f t="shared" si="22"/>
-        <v>76.111249999999998</v>
-      </c>
-      <c r="V99" s="12">
-        <f t="shared" si="20"/>
         <v>76.111249999999998</v>
       </c>
       <c r="W99" s="12">
@@ -11765,10 +12047,13 @@
         <v>177</v>
       </c>
       <c r="AH99" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI99" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI99" s="12">
+        <f t="shared" si="25"/>
+        <v>0.17600000000000002</v>
+      </c>
       <c r="AJ99" s="12"/>
       <c r="AK99" s="12"/>
       <c r="AL99" s="12"/>
@@ -11803,7 +12088,7 @@
       <c r="J100" s="8"/>
       <c r="K100" s="8"/>
       <c r="L100" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M100" s="8"/>
@@ -11814,20 +12099,20 @@
       <c r="P100" s="8"/>
       <c r="Q100" s="8"/>
       <c r="R100" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S100" s="10"/>
       <c r="T100" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U100" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V100" s="8" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U100" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V100" s="8" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W100" s="8">
@@ -11864,10 +12149,13 @@
         <v>44</v>
       </c>
       <c r="AH100" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI100" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI100" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AJ100" s="12"/>
       <c r="AK100" s="12"/>
       <c r="AL100" s="12"/>
@@ -11914,7 +12202,7 @@
         <v>114</v>
       </c>
       <c r="L101" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-6</v>
       </c>
       <c r="M101" s="12"/>
@@ -11925,20 +12213,20 @@
       <c r="P101" s="12"/>
       <c r="Q101" s="12"/>
       <c r="R101" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>21.6</v>
       </c>
       <c r="S101" s="4"/>
       <c r="T101" s="4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U101" s="12">
+        <f t="shared" si="23"/>
+        <v>11.489537037037037</v>
+      </c>
+      <c r="V101" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="U101" s="12">
-        <f t="shared" si="22"/>
-        <v>11.489537037037037</v>
-      </c>
-      <c r="V101" s="12">
-        <f t="shared" si="20"/>
         <v>11.489537037037037</v>
       </c>
       <c r="W101" s="12">
@@ -11975,10 +12263,13 @@
         <v>141</v>
       </c>
       <c r="AH101" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI101" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI101" s="12">
+        <f t="shared" si="25"/>
+        <v>1.7280000000000002</v>
+      </c>
       <c r="AJ101" s="12"/>
       <c r="AK101" s="12"/>
       <c r="AL101" s="12"/>
@@ -12025,7 +12316,7 @@
         <v>71</v>
       </c>
       <c r="L102" s="12">
-        <f t="shared" ref="L102:L129" si="27">E102-K102</f>
+        <f t="shared" ref="L102:L129" si="29">E102-K102</f>
         <v>-13</v>
       </c>
       <c r="M102" s="12"/>
@@ -12036,20 +12327,20 @@
       <c r="P102" s="12"/>
       <c r="Q102" s="12"/>
       <c r="R102" s="12">
-        <f t="shared" ref="R102:R129" si="28">E102/5</f>
+        <f t="shared" ref="R102:R129" si="30">E102/5</f>
         <v>11.6</v>
       </c>
       <c r="S102" s="4"/>
       <c r="T102" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U102" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>14.67241379310345</v>
       </c>
       <c r="V102" s="12">
-        <f t="shared" ref="V102:V129" si="29">(F102+O102+P102+Q102)/R102</f>
+        <f t="shared" ref="V102:V129" si="31">(F102+O102+P102+Q102)/R102</f>
         <v>14.67241379310345</v>
       </c>
       <c r="W102" s="12">
@@ -12086,10 +12377,13 @@
         <v>141</v>
       </c>
       <c r="AH102" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI102" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI102" s="12">
+        <f t="shared" si="25"/>
+        <v>0.92799999999999994</v>
+      </c>
       <c r="AJ102" s="12"/>
       <c r="AK102" s="12"/>
       <c r="AL102" s="12"/>
@@ -12136,7 +12430,7 @@
         <v>28</v>
       </c>
       <c r="L103" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-10</v>
       </c>
       <c r="M103" s="12"/>
@@ -12147,20 +12441,20 @@
       <c r="P103" s="12"/>
       <c r="Q103" s="12"/>
       <c r="R103" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3.6</v>
       </c>
       <c r="S103" s="4"/>
       <c r="T103" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U103" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="V103" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="W103" s="12">
@@ -12197,10 +12491,13 @@
         <v>178</v>
       </c>
       <c r="AH103" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI103" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI103" s="12">
+        <f t="shared" si="25"/>
+        <v>0.6120000000000001</v>
+      </c>
       <c r="AJ103" s="12"/>
       <c r="AK103" s="12"/>
       <c r="AL103" s="12"/>
@@ -12247,7 +12544,7 @@
         <v>66.900000000000006</v>
       </c>
       <c r="L104" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-9.4200000000000088</v>
       </c>
       <c r="M104" s="12"/>
@@ -12260,22 +12557,22 @@
       </c>
       <c r="Q104" s="12"/>
       <c r="R104" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>11.495999999999999</v>
       </c>
       <c r="S104" s="4">
         <v>100</v>
       </c>
       <c r="T104" s="4">
-        <f t="shared" ref="T104:T106" si="30">S104*0.7</f>
+        <f t="shared" ref="T104:T106" si="32">S104*0.7</f>
         <v>70</v>
       </c>
       <c r="U104" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.5562804453723036</v>
       </c>
       <c r="V104" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>-3.5327940153096735</v>
       </c>
       <c r="W104" s="12">
@@ -12310,10 +12607,13 @@
       </c>
       <c r="AG104" s="12"/>
       <c r="AH104" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>70</v>
       </c>
-      <c r="AI104" s="12"/>
+      <c r="AI104" s="12">
+        <f t="shared" si="25"/>
+        <v>11.495999999999999</v>
+      </c>
       <c r="AJ104" s="12"/>
       <c r="AK104" s="12"/>
       <c r="AL104" s="12"/>
@@ -12360,7 +12660,7 @@
         <v>97</v>
       </c>
       <c r="L105" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-18.644000000000005</v>
       </c>
       <c r="M105" s="12"/>
@@ -12371,22 +12671,22 @@
       <c r="P105" s="12"/>
       <c r="Q105" s="12"/>
       <c r="R105" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15.671199999999999</v>
       </c>
       <c r="S105" s="4">
         <v>80</v>
       </c>
       <c r="T105" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>56</v>
       </c>
       <c r="U105" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5.3602149165347903</v>
       </c>
       <c r="V105" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1.7867808463933843</v>
       </c>
       <c r="W105" s="12">
@@ -12421,10 +12721,13 @@
       </c>
       <c r="AG105" s="12"/>
       <c r="AH105" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>56</v>
       </c>
-      <c r="AI105" s="12"/>
+      <c r="AI105" s="12">
+        <f t="shared" si="25"/>
+        <v>15.671199999999999</v>
+      </c>
       <c r="AJ105" s="12"/>
       <c r="AK105" s="12"/>
       <c r="AL105" s="12"/>
@@ -12471,7 +12774,7 @@
         <v>100.2</v>
       </c>
       <c r="L106" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-44.783000000000001</v>
       </c>
       <c r="M106" s="12"/>
@@ -12484,22 +12787,22 @@
       </c>
       <c r="Q106" s="12"/>
       <c r="R106" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>11.083400000000001</v>
       </c>
       <c r="S106" s="4">
         <v>80</v>
       </c>
       <c r="T106" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>56</v>
       </c>
       <c r="U106" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6.9365898550986156</v>
       </c>
       <c r="V106" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1.8839886677373368</v>
       </c>
       <c r="W106" s="12">
@@ -12534,10 +12837,13 @@
       </c>
       <c r="AG106" s="12"/>
       <c r="AH106" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>56</v>
       </c>
-      <c r="AI106" s="12"/>
+      <c r="AI106" s="12">
+        <f t="shared" si="25"/>
+        <v>11.083400000000001</v>
+      </c>
       <c r="AJ106" s="12"/>
       <c r="AK106" s="12"/>
       <c r="AL106" s="12"/>
@@ -12572,7 +12878,7 @@
       <c r="J107" s="8"/>
       <c r="K107" s="8"/>
       <c r="L107" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M107" s="8"/>
@@ -12583,20 +12889,20 @@
       <c r="P107" s="8"/>
       <c r="Q107" s="8"/>
       <c r="R107" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="S107" s="10"/>
       <c r="T107" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U107" s="12" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V107" s="8" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W107" s="8">
@@ -12633,10 +12939,13 @@
         <v>44</v>
       </c>
       <c r="AH107" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI107" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI107" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AJ107" s="12"/>
       <c r="AK107" s="12"/>
       <c r="AL107" s="12"/>
@@ -12671,7 +12980,7 @@
       <c r="J108" s="8"/>
       <c r="K108" s="8"/>
       <c r="L108" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M108" s="8"/>
@@ -12682,20 +12991,20 @@
       <c r="P108" s="8"/>
       <c r="Q108" s="8"/>
       <c r="R108" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="S108" s="10"/>
       <c r="T108" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U108" s="12" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V108" s="8" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W108" s="8">
@@ -12732,10 +13041,13 @@
         <v>44</v>
       </c>
       <c r="AH108" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI108" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI108" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AJ108" s="12"/>
       <c r="AK108" s="12"/>
       <c r="AL108" s="12"/>
@@ -12780,7 +13092,7 @@
         <v>181</v>
       </c>
       <c r="L109" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-200</v>
       </c>
       <c r="M109" s="12"/>
@@ -12793,22 +13105,22 @@
       </c>
       <c r="Q109" s="12"/>
       <c r="R109" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-3.8</v>
       </c>
       <c r="S109" s="4">
         <v>100</v>
       </c>
       <c r="T109" s="4">
-        <f t="shared" ref="T109:T111" si="31">S109*0.7</f>
+        <f t="shared" ref="T109:T111" si="33">S109*0.7</f>
         <v>70</v>
       </c>
       <c r="U109" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-17.631578947368421</v>
       </c>
       <c r="V109" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.78947368421052444</v>
       </c>
       <c r="W109" s="12">
@@ -12843,10 +13155,13 @@
       </c>
       <c r="AG109" s="12"/>
       <c r="AH109" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
-      <c r="AI109" s="12"/>
+      <c r="AI109" s="12">
+        <f t="shared" si="25"/>
+        <v>-1.0640000000000001</v>
+      </c>
       <c r="AJ109" s="12"/>
       <c r="AK109" s="12"/>
       <c r="AL109" s="12"/>
@@ -12893,7 +13208,7 @@
         <v>131</v>
       </c>
       <c r="L110" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-128</v>
       </c>
       <c r="M110" s="12"/>
@@ -12906,22 +13221,22 @@
       </c>
       <c r="Q110" s="12"/>
       <c r="R110" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.6</v>
       </c>
       <c r="S110" s="4">
         <v>100</v>
       </c>
       <c r="T110" s="4">
+        <f t="shared" si="33"/>
+        <v>70</v>
+      </c>
+      <c r="U110" s="12">
+        <f t="shared" si="23"/>
+        <v>113.33333333333334</v>
+      </c>
+      <c r="V110" s="12">
         <f t="shared" si="31"/>
-        <v>70</v>
-      </c>
-      <c r="U110" s="12">
-        <f t="shared" si="22"/>
-        <v>113.33333333333334</v>
-      </c>
-      <c r="V110" s="12">
-        <f t="shared" si="29"/>
         <v>-3.3333333333333215</v>
       </c>
       <c r="W110" s="12">
@@ -12956,10 +13271,13 @@
       </c>
       <c r="AG110" s="12"/>
       <c r="AH110" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
-      <c r="AI110" s="12"/>
+      <c r="AI110" s="12">
+        <f t="shared" si="25"/>
+        <v>0.16800000000000001</v>
+      </c>
       <c r="AJ110" s="12"/>
       <c r="AK110" s="12"/>
       <c r="AL110" s="12"/>
@@ -13004,7 +13322,7 @@
         <v>143</v>
       </c>
       <c r="L111" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-137</v>
       </c>
       <c r="M111" s="12"/>
@@ -13017,22 +13335,22 @@
       </c>
       <c r="Q111" s="12"/>
       <c r="R111" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1.2</v>
       </c>
       <c r="S111" s="4">
         <v>70</v>
       </c>
       <c r="T111" s="4">
+        <f t="shared" si="33"/>
+        <v>49</v>
+      </c>
+      <c r="U111" s="12">
+        <f t="shared" si="23"/>
+        <v>35.833333333333343</v>
+      </c>
+      <c r="V111" s="12">
         <f t="shared" si="31"/>
-        <v>49</v>
-      </c>
-      <c r="U111" s="12">
-        <f t="shared" si="22"/>
-        <v>35.833333333333343</v>
-      </c>
-      <c r="V111" s="12">
-        <f t="shared" si="29"/>
         <v>-4.9999999999999947</v>
       </c>
       <c r="W111" s="12">
@@ -13067,10 +13385,13 @@
       </c>
       <c r="AG111" s="12"/>
       <c r="AH111" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>14</v>
       </c>
-      <c r="AI111" s="12"/>
+      <c r="AI111" s="12">
+        <f t="shared" si="25"/>
+        <v>0.33600000000000002</v>
+      </c>
       <c r="AJ111" s="12"/>
       <c r="AK111" s="12"/>
       <c r="AL111" s="12"/>
@@ -13117,7 +13438,7 @@
         <v>44</v>
       </c>
       <c r="L112" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-3</v>
       </c>
       <c r="M112" s="12"/>
@@ -13128,20 +13449,20 @@
       <c r="P112" s="12"/>
       <c r="Q112" s="12"/>
       <c r="R112" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="S112" s="4"/>
       <c r="T112" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U112" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>15.365853658536587</v>
       </c>
       <c r="V112" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15.365853658536587</v>
       </c>
       <c r="W112" s="12">
@@ -13178,10 +13499,13 @@
         <v>155</v>
       </c>
       <c r="AH112" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI112" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI112" s="12">
+        <f t="shared" si="25"/>
+        <v>0.73799999999999988</v>
+      </c>
       <c r="AJ112" s="12"/>
       <c r="AK112" s="12"/>
       <c r="AL112" s="12"/>
@@ -13226,7 +13550,7 @@
         <v>30</v>
       </c>
       <c r="L113" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.17800000000000082</v>
       </c>
       <c r="M113" s="12"/>
@@ -13237,20 +13561,20 @@
       <c r="P113" s="12"/>
       <c r="Q113" s="12"/>
       <c r="R113" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>6.0356000000000005</v>
       </c>
       <c r="S113" s="4"/>
       <c r="T113" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U113" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>21.133143349459868</v>
       </c>
       <c r="V113" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>21.133143349459868</v>
       </c>
       <c r="W113" s="12">
@@ -13287,10 +13611,13 @@
         <v>41</v>
       </c>
       <c r="AH113" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI113" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI113" s="12">
+        <f t="shared" si="25"/>
+        <v>6.0356000000000005</v>
+      </c>
       <c r="AJ113" s="12"/>
       <c r="AK113" s="12"/>
       <c r="AL113" s="12"/>
@@ -13337,7 +13664,7 @@
         <v>37.5</v>
       </c>
       <c r="L114" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-9.8999999999996646E-2</v>
       </c>
       <c r="M114" s="12"/>
@@ -13348,20 +13675,20 @@
       <c r="P114" s="12"/>
       <c r="Q114" s="12"/>
       <c r="R114" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7.4802000000000008</v>
       </c>
       <c r="S114" s="4"/>
       <c r="T114" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U114" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>24.335071254779283</v>
       </c>
       <c r="V114" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>24.335071254779283</v>
       </c>
       <c r="W114" s="12">
@@ -13398,10 +13725,13 @@
         <v>41</v>
       </c>
       <c r="AH114" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI114" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI114" s="12">
+        <f t="shared" si="25"/>
+        <v>7.4802000000000008</v>
+      </c>
       <c r="AJ114" s="12"/>
       <c r="AK114" s="12"/>
       <c r="AL114" s="12"/>
@@ -13448,7 +13778,7 @@
         <v>40</v>
       </c>
       <c r="L115" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-2</v>
       </c>
       <c r="M115" s="12"/>
@@ -13459,20 +13789,20 @@
       <c r="P115" s="12"/>
       <c r="Q115" s="12"/>
       <c r="R115" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7.6</v>
       </c>
       <c r="S115" s="4"/>
       <c r="T115" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U115" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>15.657894736842106</v>
       </c>
       <c r="V115" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15.657894736842106</v>
       </c>
       <c r="W115" s="12">
@@ -13509,10 +13839,13 @@
         <v>141</v>
       </c>
       <c r="AH115" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI115" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI115" s="12">
+        <f t="shared" si="25"/>
+        <v>0.68399999999999994</v>
+      </c>
       <c r="AJ115" s="12"/>
       <c r="AK115" s="12"/>
       <c r="AL115" s="12"/>
@@ -13559,7 +13892,7 @@
         <v>62</v>
       </c>
       <c r="L116" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-1</v>
       </c>
       <c r="M116" s="12"/>
@@ -13570,23 +13903,23 @@
       <c r="P116" s="12"/>
       <c r="Q116" s="12"/>
       <c r="R116" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>12.2</v>
       </c>
       <c r="S116" s="4">
-        <f t="shared" ref="S116:S128" si="32">11*R116-Q116-P116-O116-F116</f>
+        <f t="shared" ref="S116:S128" si="34">11*R116-Q116-P116-O116-F116</f>
         <v>33.199999999999989</v>
       </c>
       <c r="T116" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>33.199999999999989</v>
       </c>
       <c r="U116" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="V116" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>8.278688524590164</v>
       </c>
       <c r="W116" s="12">
@@ -13623,10 +13956,13 @@
         <v>141</v>
       </c>
       <c r="AH116" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
-      <c r="AI116" s="12"/>
+      <c r="AI116" s="12">
+        <f t="shared" si="25"/>
+        <v>1.0979999999999999</v>
+      </c>
       <c r="AJ116" s="12"/>
       <c r="AK116" s="12"/>
       <c r="AL116" s="12"/>
@@ -13673,7 +14009,7 @@
         <v>62.2</v>
       </c>
       <c r="L117" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5.0459999999999923</v>
       </c>
       <c r="M117" s="12"/>
@@ -13684,20 +14020,20 @@
       <c r="P117" s="12"/>
       <c r="Q117" s="12"/>
       <c r="R117" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>13.449199999999999</v>
       </c>
       <c r="S117" s="4"/>
       <c r="T117" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U117" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>13.820608809445908</v>
       </c>
       <c r="V117" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>13.820608809445908</v>
       </c>
       <c r="W117" s="12">
@@ -13732,10 +14068,13 @@
       </c>
       <c r="AG117" s="12"/>
       <c r="AH117" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI117" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI117" s="12">
+        <f t="shared" si="25"/>
+        <v>13.449199999999999</v>
+      </c>
       <c r="AJ117" s="12"/>
       <c r="AK117" s="12"/>
       <c r="AL117" s="12"/>
@@ -13782,7 +14121,7 @@
         <v>115</v>
       </c>
       <c r="L118" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-1.7729999999999961</v>
       </c>
       <c r="M118" s="12"/>
@@ -13793,23 +14132,23 @@
       <c r="P118" s="12"/>
       <c r="Q118" s="12"/>
       <c r="R118" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>22.645400000000002</v>
       </c>
       <c r="S118" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>89.335400000000021</v>
       </c>
       <c r="T118" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>89.335400000000021</v>
       </c>
       <c r="U118" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="V118" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>7.055031043832301</v>
       </c>
       <c r="W118" s="12">
@@ -13844,10 +14183,13 @@
       </c>
       <c r="AG118" s="12"/>
       <c r="AH118" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>89</v>
       </c>
-      <c r="AI118" s="12"/>
+      <c r="AI118" s="12">
+        <f t="shared" si="25"/>
+        <v>22.645400000000002</v>
+      </c>
       <c r="AJ118" s="12"/>
       <c r="AK118" s="12"/>
       <c r="AL118" s="12"/>
@@ -13894,7 +14236,7 @@
         <v>33.799999999999997</v>
       </c>
       <c r="L119" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>9.4990000000000023</v>
       </c>
       <c r="M119" s="12"/>
@@ -13905,7 +14247,7 @@
       <c r="P119" s="12"/>
       <c r="Q119" s="12"/>
       <c r="R119" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>8.6598000000000006</v>
       </c>
       <c r="S119" s="4">
@@ -13913,15 +14255,15 @@
         <v>48.038400000000003</v>
       </c>
       <c r="T119" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>48.038400000000003</v>
       </c>
       <c r="U119" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>9</v>
       </c>
       <c r="V119" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>3.4527125337767619</v>
       </c>
       <c r="W119" s="12">
@@ -13956,10 +14298,13 @@
       </c>
       <c r="AG119" s="12"/>
       <c r="AH119" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>48</v>
       </c>
-      <c r="AI119" s="12"/>
+      <c r="AI119" s="12">
+        <f t="shared" si="25"/>
+        <v>8.6598000000000006</v>
+      </c>
       <c r="AJ119" s="12"/>
       <c r="AK119" s="12"/>
       <c r="AL119" s="12"/>
@@ -14006,7 +14351,7 @@
         <v>874.5</v>
       </c>
       <c r="L120" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-13.657000000000039</v>
       </c>
       <c r="M120" s="12"/>
@@ -14019,23 +14364,23 @@
         <v>200</v>
       </c>
       <c r="R120" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>172.1686</v>
       </c>
       <c r="S120" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>30.169026000000031</v>
       </c>
       <c r="T120" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>30.169026000000031</v>
       </c>
       <c r="U120" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="V120" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>10.82477045175485</v>
       </c>
       <c r="W120" s="12">
@@ -14070,10 +14415,13 @@
       </c>
       <c r="AG120" s="12"/>
       <c r="AH120" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>30</v>
       </c>
-      <c r="AI120" s="12"/>
+      <c r="AI120" s="12">
+        <f t="shared" si="25"/>
+        <v>172.1686</v>
+      </c>
       <c r="AJ120" s="12"/>
       <c r="AK120" s="12"/>
       <c r="AL120" s="12"/>
@@ -14120,7 +14468,7 @@
         <v>158</v>
       </c>
       <c r="L121" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-14</v>
       </c>
       <c r="M121" s="12"/>
@@ -14131,7 +14479,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
       <c r="R121" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>28.8</v>
       </c>
       <c r="S121" s="4">
@@ -14142,11 +14490,11 @@
         <v>140</v>
       </c>
       <c r="U121" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5.7986111111111107</v>
       </c>
       <c r="V121" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.9375</v>
       </c>
       <c r="W121" s="12">
@@ -14183,10 +14531,13 @@
         <v>165</v>
       </c>
       <c r="AH121" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>35</v>
       </c>
-      <c r="AI121" s="12"/>
+      <c r="AI121" s="12">
+        <f t="shared" si="25"/>
+        <v>7.2</v>
+      </c>
       <c r="AJ121" s="12"/>
       <c r="AK121" s="12"/>
       <c r="AL121" s="12"/>
@@ -14235,7 +14586,7 @@
         <v>28</v>
       </c>
       <c r="L122" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>54</v>
       </c>
       <c r="M122" s="12"/>
@@ -14246,23 +14597,23 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
       <c r="R122" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>16.399999999999999</v>
       </c>
       <c r="S122" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>87.399999999999977</v>
       </c>
       <c r="T122" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>87.399999999999977</v>
       </c>
       <c r="U122" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="V122" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>5.6707317073170733</v>
       </c>
       <c r="W122" s="12">
@@ -14299,10 +14650,13 @@
         <v>165</v>
       </c>
       <c r="AH122" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>28</v>
       </c>
-      <c r="AI122" s="12"/>
+      <c r="AI122" s="12">
+        <f t="shared" si="25"/>
+        <v>5.33</v>
+      </c>
       <c r="AJ122" s="12"/>
       <c r="AK122" s="12"/>
       <c r="AL122" s="12"/>
@@ -14347,7 +14701,7 @@
         <v>386</v>
       </c>
       <c r="L123" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>2</v>
       </c>
       <c r="M123" s="12"/>
@@ -14358,7 +14712,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
       <c r="R123" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>77.599999999999994</v>
       </c>
       <c r="S123" s="4">
@@ -14366,15 +14720,15 @@
         <v>480.4</v>
       </c>
       <c r="T123" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>480.4</v>
       </c>
       <c r="U123" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>9</v>
       </c>
       <c r="V123" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>2.8092783505154642</v>
       </c>
       <c r="W123" s="12">
@@ -14411,10 +14765,13 @@
         <v>165</v>
       </c>
       <c r="AH123" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>120</v>
       </c>
-      <c r="AI123" s="12"/>
+      <c r="AI123" s="12">
+        <f t="shared" si="25"/>
+        <v>19.399999999999999</v>
+      </c>
       <c r="AJ123" s="12"/>
       <c r="AK123" s="12"/>
       <c r="AL123" s="12"/>
@@ -14461,7 +14818,7 @@
         <v>295</v>
       </c>
       <c r="L124" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-64</v>
       </c>
       <c r="M124" s="12"/>
@@ -14474,22 +14831,22 @@
       </c>
       <c r="Q124" s="12"/>
       <c r="R124" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>46.2</v>
       </c>
       <c r="S124" s="4">
         <v>120</v>
       </c>
       <c r="T124" s="4">
-        <f t="shared" ref="T124:T125" si="33">S124*0.7</f>
+        <f t="shared" ref="T124:T125" si="35">S124*0.7</f>
         <v>84</v>
       </c>
       <c r="U124" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1.4718614718614718</v>
       </c>
       <c r="V124" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>-0.34632034632034631</v>
       </c>
       <c r="W124" s="12">
@@ -14524,10 +14881,13 @@
       </c>
       <c r="AG124" s="12"/>
       <c r="AH124" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>25</v>
       </c>
-      <c r="AI124" s="12"/>
+      <c r="AI124" s="12">
+        <f t="shared" si="25"/>
+        <v>13.860000000000001</v>
+      </c>
       <c r="AJ124" s="12"/>
       <c r="AK124" s="12"/>
       <c r="AL124" s="12"/>
@@ -14574,7 +14934,7 @@
         <v>117</v>
       </c>
       <c r="L125" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-125</v>
       </c>
       <c r="M125" s="12"/>
@@ -14587,22 +14947,22 @@
       </c>
       <c r="Q125" s="12"/>
       <c r="R125" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-1.6</v>
       </c>
       <c r="S125" s="4">
         <v>70</v>
       </c>
       <c r="T125" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>49</v>
       </c>
       <c r="U125" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-32.5</v>
       </c>
       <c r="V125" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>-1.875</v>
       </c>
       <c r="W125" s="12">
@@ -14637,10 +14997,13 @@
       </c>
       <c r="AG125" s="12"/>
       <c r="AH125" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>15</v>
       </c>
-      <c r="AI125" s="12"/>
+      <c r="AI125" s="12">
+        <f t="shared" si="25"/>
+        <v>-0.48</v>
+      </c>
       <c r="AJ125" s="12"/>
       <c r="AK125" s="12"/>
       <c r="AL125" s="12"/>
@@ -14685,7 +15048,7 @@
         <v>17.2</v>
       </c>
       <c r="L126" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-2.2309999999999999</v>
       </c>
       <c r="M126" s="12"/>
@@ -14696,20 +15059,20 @@
       <c r="P126" s="12"/>
       <c r="Q126" s="12"/>
       <c r="R126" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2.9937999999999998</v>
       </c>
       <c r="S126" s="4"/>
       <c r="T126" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U126" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11.299485603580735</v>
       </c>
       <c r="V126" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11.299485603580735</v>
       </c>
       <c r="W126" s="12">
@@ -14744,10 +15107,13 @@
       </c>
       <c r="AG126" s="12"/>
       <c r="AH126" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI126" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI126" s="12">
+        <f t="shared" si="25"/>
+        <v>2.9937999999999998</v>
+      </c>
       <c r="AJ126" s="12"/>
       <c r="AK126" s="12"/>
       <c r="AL126" s="12"/>
@@ -14794,7 +15160,7 @@
         <v>188</v>
       </c>
       <c r="L127" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-21</v>
       </c>
       <c r="M127" s="12"/>
@@ -14807,7 +15173,7 @@
       </c>
       <c r="Q127" s="12"/>
       <c r="R127" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>33.4</v>
       </c>
       <c r="S127" s="4">
@@ -14818,11 +15184,11 @@
         <v>70</v>
       </c>
       <c r="U127" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1.8862275449101797</v>
       </c>
       <c r="V127" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>-0.20958083832335331</v>
       </c>
       <c r="W127" s="12">
@@ -14857,10 +15223,13 @@
       </c>
       <c r="AG127" s="12"/>
       <c r="AH127" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>21</v>
       </c>
-      <c r="AI127" s="12"/>
+      <c r="AI127" s="12">
+        <f t="shared" si="25"/>
+        <v>10.02</v>
+      </c>
       <c r="AJ127" s="12"/>
       <c r="AK127" s="12"/>
       <c r="AL127" s="12"/>
@@ -14907,7 +15276,7 @@
         <v>38</v>
       </c>
       <c r="L128" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-4</v>
       </c>
       <c r="M128" s="12"/>
@@ -14920,23 +15289,23 @@
       </c>
       <c r="Q128" s="12"/>
       <c r="R128" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>6.8</v>
       </c>
       <c r="S128" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>34</v>
       </c>
       <c r="T128" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>34</v>
       </c>
       <c r="U128" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="V128" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>6</v>
       </c>
       <c r="W128" s="12">
@@ -14971,10 +15340,13 @@
       </c>
       <c r="AG128" s="12"/>
       <c r="AH128" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4</v>
       </c>
-      <c r="AI128" s="12"/>
+      <c r="AI128" s="12">
+        <f t="shared" si="25"/>
+        <v>0.81599999999999995</v>
+      </c>
       <c r="AJ128" s="12"/>
       <c r="AK128" s="12"/>
       <c r="AL128" s="12"/>
@@ -15019,7 +15391,7 @@
         <v>74</v>
       </c>
       <c r="L129" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-12</v>
       </c>
       <c r="M129" s="8"/>
@@ -15030,20 +15402,20 @@
       <c r="P129" s="8"/>
       <c r="Q129" s="8"/>
       <c r="R129" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>12.4</v>
       </c>
       <c r="S129" s="10"/>
       <c r="T129" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U129" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-5.0806451612903221</v>
       </c>
       <c r="V129" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>-5.0806451612903221</v>
       </c>
       <c r="W129" s="8">
@@ -15078,10 +15450,13 @@
       </c>
       <c r="AG129" s="8"/>
       <c r="AH129" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AI129" s="12"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AI129" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AJ129" s="12"/>
       <c r="AK129" s="12"/>
       <c r="AL129" s="12"/>
